--- a/database/event/2763/event_2763_evp_summary.xlsx
+++ b/database/event/2763/event_2763_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1183</v>
+        <v>6.6552</v>
       </c>
       <c r="C2" t="n">
-        <v>2.486</v>
+        <v>2.7042</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0503</v>
+        <v>2.2075</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1183</v>
+        <v>6.6552</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2063</v>
+        <v>2.7432</v>
       </c>
       <c r="G2" t="n">
         <v>3.912</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2063</v>
+        <v>2.7432</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7883</v>
+        <v>2.2235</v>
       </c>
       <c r="J2" t="n">
         <v>3.912</v>
@@ -529,7 +529,7 @@
         <v>185</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7003</v>
+        <v>6.1355</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -548,7 +548,7 @@
         <v>2.086</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6525</v>
+        <v>1.6014</v>
       </c>
       <c r="E3" t="n">
         <v>5.1337</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8308</v>
+        <v>4.205</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5566</v>
+        <v>1.7086</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1262</v>
+        <v>1.2314</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8308</v>
+        <v>4.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9922</v>
+        <v>3.0492</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8386</v>
+        <v>1.1558</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9922</v>
+        <v>3.0492</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4253</v>
+        <v>2.4715</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8386</v>
+        <v>1.1558</v>
       </c>
       <c r="K4" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="L4" t="n">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2639</v>
+        <v>3.6273</v>
       </c>
       <c r="N4" t="n">
-        <v>218</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7493</v>
+        <v>3.8308</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5234</v>
+        <v>1.5566</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0933</v>
+        <v>1.0823</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7493</v>
+        <v>3.8308</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5935</v>
+        <v>2.9922</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1558</v>
+        <v>0.8386</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5935</v>
+        <v>2.9922</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1021</v>
+        <v>2.4253</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1558</v>
+        <v>0.8386</v>
       </c>
       <c r="K5" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="L5" t="n">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2579</v>
+        <v>3.2639</v>
       </c>
       <c r="N5" t="n">
-        <v>256</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0526</v>
+        <v>3.339</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2404</v>
+        <v>1.3567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8118</v>
+        <v>0.8863</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0526</v>
+        <v>3.339</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0713</v>
+        <v>2.7953</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0187</v>
+        <v>0.5437</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0713</v>
+        <v>2.7953</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4893</v>
+        <v>2.2657</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0187</v>
+        <v>0.5437</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4706</v>
+        <v>2.8094</v>
       </c>
       <c r="N6" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8247</v>
+        <v>3.0553</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1478</v>
+        <v>1.2415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7198</v>
+        <v>0.7733</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8247</v>
+        <v>3.0553</v>
       </c>
       <c r="F7" t="n">
-        <v>2.281</v>
+        <v>3.074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5437</v>
+        <v>-0.0187</v>
       </c>
       <c r="H7" t="n">
-        <v>2.281</v>
+        <v>3.074</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8488</v>
+        <v>2.4916</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5437</v>
+        <v>-0.0187</v>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3925</v>
+        <v>2.4729</v>
       </c>
       <c r="N7" t="n">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6721</v>
+        <v>2.7377</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0857</v>
+        <v>1.1124</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6581</v>
+        <v>0.6468</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6721</v>
+        <v>2.7377</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7394</v>
+        <v>1.805</v>
       </c>
       <c r="G8" t="n">
         <v>0.9327</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7394</v>
+        <v>1.805</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4098</v>
+        <v>1.463</v>
       </c>
       <c r="J8" t="n">
         <v>0.9327</v>
@@ -805,7 +805,7 @@
         <v>185</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3425</v>
+        <v>2.3957</v>
       </c>
       <c r="N8" t="n">
         <v>232</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5385</v>
+        <v>2.5291</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0315</v>
+        <v>1.0276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6041</v>
+        <v>0.5637</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5385</v>
+        <v>2.5291</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5385</v>
+        <v>2.5291</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5385</v>
+        <v>2.5291</v>
       </c>
       <c r="I9" t="n">
         <v>2.5504</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2946</v>
+        <v>2.5217</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9324</v>
+        <v>1.0246</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5056</v>
+        <v>0.5607</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2946</v>
+        <v>2.5217</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6176</v>
+        <v>2.9024</v>
       </c>
       <c r="G10" t="n">
-        <v>1.677</v>
+        <v>-0.3807</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6176</v>
+        <v>2.9024</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5006</v>
+        <v>2.3525</v>
       </c>
       <c r="J10" t="n">
-        <v>1.677</v>
+        <v>-0.3807</v>
       </c>
       <c r="K10" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1776</v>
+        <v>1.9718</v>
       </c>
       <c r="N10" t="n">
-        <v>256</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2875</v>
+        <v>2.2946</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9295</v>
+        <v>0.9324</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5027</v>
+        <v>0.4703</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2875</v>
+        <v>2.2946</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2875</v>
+        <v>0.6176</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.677</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2875</v>
+        <v>0.6176</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2981</v>
+        <v>0.5006</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.677</v>
       </c>
       <c r="K11" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2981</v>
+        <v>2.1776</v>
       </c>
       <c r="N11" t="n">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9588</v>
+        <v>2.279</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3699</v>
+        <v>0.464</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9588</v>
+        <v>2.279</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3395</v>
+        <v>2.279</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3807</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3395</v>
+        <v>2.279</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8962</v>
+        <v>2.2981</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3807</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5155</v>
+        <v>2.2981</v>
       </c>
       <c r="N12" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5513</v>
+        <v>1.8738</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6303</v>
+        <v>0.7614</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2053</v>
+        <v>0.3026</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5513</v>
+        <v>1.8738</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5513</v>
+        <v>2.7084</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.8346</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5513</v>
+        <v>2.7084</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5585</v>
+        <v>2.1952</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.8346</v>
       </c>
       <c r="K13" t="n">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5585</v>
+        <v>1.3606</v>
       </c>
       <c r="N13" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -1054,7 +1054,7 @@
         <v>0.628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.203</v>
+        <v>0.1719</v>
       </c>
       <c r="E14" t="n">
         <v>1.5456</v>
@@ -1090,124 +1090,124 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5044</v>
+        <v>1.5455</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6113</v>
+        <v>0.628</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1864</v>
+        <v>0.1718</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5044</v>
+        <v>1.5455</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5281</v>
+        <v>1.5455</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0237</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5281</v>
+        <v>1.5455</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2386</v>
+        <v>1.5585</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0237</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="L15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2149</v>
+        <v>1.5585</v>
       </c>
       <c r="N15" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4988</v>
+        <v>1.513</v>
       </c>
       <c r="C16" t="n">
-        <v>0.609</v>
+        <v>0.6148</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1841</v>
+        <v>0.1589</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4988</v>
+        <v>1.513</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4988</v>
+        <v>1.5367</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.0237</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4988</v>
+        <v>1.5367</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4988</v>
+        <v>1.2455</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.0237</v>
       </c>
       <c r="K16" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4988</v>
+        <v>1.2218</v>
       </c>
       <c r="N16" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5764</v>
+        <v>0.609</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1517</v>
+        <v>0.1532</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4185</v>
+        <v>1.4988</v>
       </c>
       <c r="N17" t="n">
         <v>119</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3989</v>
+        <v>1.4185</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5684</v>
+        <v>0.5764</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1438</v>
+        <v>0.1212</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3989</v>
+        <v>1.4185</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2335</v>
+        <v>1.4185</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8346</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2335</v>
+        <v>1.4185</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8103</v>
+        <v>1.4185</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8346</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="L18" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9757</v>
+        <v>1.4185</v>
       </c>
       <c r="N18" t="n">
-        <v>232</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>0.5239</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="E19" t="n">
         <v>1.2893</v>
@@ -1330,7 +1330,7 @@
         <v>0.3399</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0834</v>
+        <v>-0.1106</v>
       </c>
       <c r="E20" t="n">
         <v>0.8365</v>
@@ -1376,7 +1376,7 @@
         <v>0.321</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1022</v>
+        <v>-0.1291</v>
       </c>
       <c r="E21" t="n">
         <v>0.7901</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4289</v>
+        <v>0.5745</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1743</v>
+        <v>0.2334</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2481</v>
+        <v>-0.215</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4289</v>
+        <v>0.5745</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.5745</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2067</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.5745</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5152</v>
+        <v>0.5745</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2067</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3085</v>
+        <v>0.5745</v>
       </c>
       <c r="N22" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3848</v>
+        <v>0.4289</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1564</v>
+        <v>0.1743</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2659</v>
+        <v>-0.273</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3848</v>
+        <v>0.4289</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3848</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.2067</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3848</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3848</v>
+        <v>0.5152</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.2067</v>
       </c>
       <c r="K23" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3848</v>
+        <v>0.3085</v>
       </c>
       <c r="N23" t="n">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="C24" t="n">
-        <v>0.15</v>
+        <v>0.1494</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2723</v>
+        <v>-0.2974</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="I24" t="n">
         <v>0.3708</v>
@@ -1560,7 +1560,7 @@
         <v>0.1419</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2803</v>
+        <v>-0.3048</v>
       </c>
       <c r="E25" t="n">
         <v>0.3492</v>
@@ -1606,7 +1606,7 @@
         <v>0.1372</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2849</v>
+        <v>-0.3094</v>
       </c>
       <c r="E26" t="n">
         <v>0.3377</v>
@@ -1652,7 +1652,7 @@
         <v>0.1262</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2959</v>
+        <v>-0.3202</v>
       </c>
       <c r="E27" t="n">
         <v>0.3106</v>
@@ -1698,7 +1698,7 @@
         <v>0.1195</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3026</v>
+        <v>-0.3268</v>
       </c>
       <c r="E28" t="n">
         <v>0.294</v>
@@ -1744,7 +1744,7 @@
         <v>0.0806</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3413</v>
+        <v>-0.3649</v>
       </c>
       <c r="E29" t="n">
         <v>0.1983</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0325</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4536</v>
+        <v>-0.4757</v>
       </c>
       <c r="E30" t="n">
         <v>-0.0799</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2513</v>
+        <v>-0.2504</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1021</v>
+        <v>-0.1017</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5229</v>
+        <v>-0.5437</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2513</v>
+        <v>-0.2504</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2513</v>
+        <v>-0.2504</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2513</v>
+        <v>-0.2504</v>
       </c>
       <c r="I31" t="n">
         <v>-0.2525</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1098</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5306</v>
+        <v>-0.5516</v>
       </c>
       <c r="E32" t="n">
         <v>-0.2703</v>
@@ -1928,7 +1928,7 @@
         <v>-0.206</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6261</v>
+        <v>-0.6459</v>
       </c>
       <c r="E33" t="n">
         <v>-0.5069</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2275</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6475</v>
+        <v>-0.6669</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5598</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2444</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6644</v>
+        <v>-0.6836</v>
       </c>
       <c r="E35" t="n">
         <v>-0.6016</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3362</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7556</v>
+        <v>-0.7735</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8274</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4476</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8663</v>
+        <v>-0.8827</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1015</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6046</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0225</v>
+        <v>-1.0367</v>
       </c>
       <c r="E38" t="n">
         <v>-1.488</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6346000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0523</v>
+        <v>-1.0661</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5617</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6422</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0598</v>
+        <v>-1.0736</v>
       </c>
       <c r="E40" t="n">
         <v>-1.5805</v>
@@ -2296,7 +2296,7 @@
         <v>-0.675</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0925</v>
+        <v>-1.1057</v>
       </c>
       <c r="E41" t="n">
         <v>-1.6612</v>

--- a/database/event/2763/event_2763_evp_summary.xlsx
+++ b/database/event/2763/event_2763_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6552</v>
+        <v>6.2732</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7042</v>
+        <v>2.549</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2075</v>
+        <v>2.194</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6552</v>
+        <v>6.2732</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7432</v>
+        <v>2.7087</v>
       </c>
       <c r="G2" t="n">
-        <v>3.912</v>
+        <v>3.5645</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7432</v>
+        <v>4.0575</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2235</v>
+        <v>2.1097</v>
       </c>
       <c r="J2" t="n">
-        <v>3.912</v>
+        <v>3.5645</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>185</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1355</v>
+        <v>5.6742</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1337</v>
+        <v>5.0448</v>
       </c>
       <c r="C3" t="n">
-        <v>2.086</v>
+        <v>2.0498</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6014</v>
+        <v>1.6395</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1337</v>
+        <v>5.0448</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6433</v>
+        <v>2.6736</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4904</v>
+        <v>2.3712</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6433</v>
+        <v>3.9336</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1425</v>
+        <v>2.0453</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4904</v>
+        <v>2.3712</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>154</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6329</v>
+        <v>4.4165</v>
       </c>
       <c r="N3" t="n">
         <v>256</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.205</v>
+        <v>3.9785</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7086</v>
+        <v>1.6166</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2314</v>
+        <v>1.1581</v>
       </c>
       <c r="E4" t="n">
-        <v>4.205</v>
+        <v>3.9785</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0492</v>
+        <v>2.8454</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1558</v>
+        <v>1.1331</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0492</v>
+        <v>4.5392</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4715</v>
+        <v>2.3602</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1558</v>
+        <v>1.1331</v>
       </c>
       <c r="K4" t="n">
         <v>102</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6273</v>
+        <v>3.4933</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8308</v>
+        <v>3.7796</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5566</v>
+        <v>1.5358</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0823</v>
+        <v>1.0683</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8308</v>
+        <v>3.7796</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9922</v>
+        <v>2.9529</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8386</v>
+        <v>0.8267</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9922</v>
+        <v>4.9179</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4253</v>
+        <v>2.5571</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8386</v>
+        <v>0.8267</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2639</v>
+        <v>3.3838</v>
       </c>
       <c r="N5" t="n">
         <v>218</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.339</v>
+        <v>3.4509</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3567</v>
+        <v>1.4022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8863</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.339</v>
+        <v>3.4509</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7953</v>
+        <v>2.4399</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5437</v>
+        <v>1.011</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7953</v>
+        <v>3.1103</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2657</v>
+        <v>1.6172</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5437</v>
+        <v>1.011</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>185</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8094</v>
+        <v>2.6282</v>
       </c>
       <c r="N6" t="n">
         <v>232</v>
@@ -722,461 +722,461 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0553</v>
+        <v>3.3252</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2415</v>
+        <v>1.3511</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7733</v>
+        <v>0.8631</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0553</v>
+        <v>3.3252</v>
       </c>
       <c r="F7" t="n">
-        <v>3.074</v>
+        <v>2.7543</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0187</v>
+        <v>0.5709</v>
       </c>
       <c r="H7" t="n">
-        <v>3.074</v>
+        <v>4.2181</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4916</v>
+        <v>2.1932</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0187</v>
+        <v>0.5709</v>
       </c>
       <c r="K7" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4729</v>
+        <v>2.7641</v>
       </c>
       <c r="N7" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7377</v>
+        <v>3.0864</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1124</v>
+        <v>1.2541</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6468</v>
+        <v>0.7553</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7377</v>
+        <v>3.0864</v>
       </c>
       <c r="F8" t="n">
-        <v>1.805</v>
+        <v>3.0864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9327</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.805</v>
+        <v>3.4175</v>
       </c>
       <c r="I8" t="n">
-        <v>1.463</v>
+        <v>3.5581</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9327</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="L8" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3957</v>
+        <v>3.5581</v>
       </c>
       <c r="N8" t="n">
-        <v>232</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5291</v>
+        <v>3.0375</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0276</v>
+        <v>1.2342</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5637</v>
+        <v>0.7333</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5291</v>
+        <v>3.0375</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5291</v>
+        <v>1.6876</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.3499</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5291</v>
+        <v>1.6876</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5504</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.3499</v>
       </c>
       <c r="K9" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5504</v>
+        <v>2.2274</v>
       </c>
       <c r="N9" t="n">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5217</v>
+        <v>2.9798</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0246</v>
+        <v>1.2108</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5607</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5217</v>
+        <v>2.9798</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9024</v>
+        <v>2.9171</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3807</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9024</v>
+        <v>4.7916</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3525</v>
+        <v>2.4914</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3807</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="L10" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9718</v>
+        <v>2.5541</v>
       </c>
       <c r="N10" t="n">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2946</v>
+        <v>2.6829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9324</v>
+        <v>1.0901</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4703</v>
+        <v>0.5732</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2946</v>
+        <v>2.6829</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6176</v>
+        <v>2.6829</v>
       </c>
       <c r="G11" t="n">
-        <v>1.677</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6176</v>
+        <v>2.6829</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5006</v>
+        <v>2.7932</v>
       </c>
       <c r="J11" t="n">
-        <v>1.677</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="L11" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1776</v>
+        <v>2.7932</v>
       </c>
       <c r="N11" t="n">
-        <v>256</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.279</v>
+        <v>2.4828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.926</v>
+        <v>1.0088</v>
       </c>
       <c r="D12" t="n">
-        <v>0.464</v>
+        <v>0.4828</v>
       </c>
       <c r="E12" t="n">
-        <v>2.279</v>
+        <v>2.4828</v>
       </c>
       <c r="F12" t="n">
-        <v>2.279</v>
+        <v>2.7492</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="H12" t="n">
-        <v>2.279</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2981</v>
+        <v>2.1838</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="K12" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2981</v>
+        <v>1.9174</v>
       </c>
       <c r="N12" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8738</v>
+        <v>2.2536</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7614</v>
+        <v>0.9157</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3026</v>
+        <v>0.3794</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8738</v>
+        <v>2.2536</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7084</v>
+        <v>2.2536</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8346</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7084</v>
+        <v>2.2536</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1952</v>
+        <v>2.2536</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8346</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="L13" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3606</v>
+        <v>2.2536</v>
       </c>
       <c r="N13" t="n">
-        <v>232</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5456</v>
+        <v>2.2241</v>
       </c>
       <c r="C14" t="n">
-        <v>0.628</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1719</v>
+        <v>0.3661</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5456</v>
+        <v>2.2241</v>
       </c>
       <c r="F14" t="n">
-        <v>1.054</v>
+        <v>2.2253</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4916</v>
+        <v>-0.0012</v>
       </c>
       <c r="H14" t="n">
-        <v>1.054</v>
+        <v>2.3542</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8542999999999999</v>
+        <v>1.2241</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4916</v>
+        <v>-0.0012</v>
       </c>
       <c r="K14" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3459</v>
+        <v>1.2229</v>
       </c>
       <c r="N14" t="n">
-        <v>256</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5455</v>
+        <v>2.2035</v>
       </c>
       <c r="C15" t="n">
-        <v>0.628</v>
+        <v>0.8953</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1718</v>
+        <v>0.3568</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5455</v>
+        <v>2.2035</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5455</v>
+        <v>1.9875</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5455</v>
+        <v>1.9875</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5585</v>
+        <v>1.0334</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="K15" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5585</v>
+        <v>1.2494</v>
       </c>
       <c r="N15" t="n">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.513</v>
+        <v>1.9395</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6148</v>
+        <v>0.7881</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1589</v>
+        <v>0.2376</v>
       </c>
       <c r="E16" t="n">
-        <v>1.513</v>
+        <v>1.9395</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5367</v>
+        <v>2.4512</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0237</v>
+        <v>-0.5117</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5367</v>
+        <v>3.1503</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2455</v>
+        <v>1.638</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0237</v>
+        <v>-0.5117</v>
       </c>
       <c r="K16" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2218</v>
+        <v>1.1263</v>
       </c>
       <c r="N16" t="n">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="C17" t="n">
-        <v>0.609</v>
+        <v>0.7784</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1532</v>
+        <v>0.2268</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4988</v>
+        <v>1.9156</v>
       </c>
       <c r="N17" t="n">
         <v>119</v>
@@ -1228,81 +1228,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4185</v>
+        <v>1.9012</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5764</v>
+        <v>0.7725</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1212</v>
+        <v>0.2203</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4185</v>
+        <v>1.9012</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4185</v>
+        <v>2.7086</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.8074</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4185</v>
+        <v>4.0571</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4185</v>
+        <v>2.1095</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.8074</v>
       </c>
       <c r="K18" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4185</v>
+        <v>1.3021</v>
       </c>
       <c r="N18" t="n">
-        <v>119</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2893</v>
+        <v>1.765</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5239</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0697</v>
+        <v>0.1588</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2893</v>
+        <v>1.765</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0821</v>
+        <v>1.7596</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7927999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0821</v>
+        <v>1.7596</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6876</v>
+        <v>0.9149</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7927999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="K19" t="n">
         <v>132</v>
@@ -1311,7 +1311,7 @@
         <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8948</v>
+        <v>0.9203</v>
       </c>
       <c r="N19" t="n">
         <v>218</v>
@@ -1320,185 +1320,185 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8365</v>
+        <v>1.6242</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3399</v>
+        <v>0.66</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1106</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8365</v>
+        <v>1.6242</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8365</v>
+        <v>1.6242</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8365</v>
+        <v>1.6242</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8365</v>
+        <v>1.691</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8365</v>
+        <v>1.691</v>
       </c>
       <c r="N20" t="n">
-        <v>119</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7901</v>
+        <v>1.4155</v>
       </c>
       <c r="C21" t="n">
-        <v>0.321</v>
+        <v>0.5752</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1291</v>
+        <v>0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7901</v>
+        <v>1.4155</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7901</v>
+        <v>1.093</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.3225</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7901</v>
+        <v>1.093</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7901</v>
+        <v>0.5683</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.3225</v>
       </c>
       <c r="K21" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7901</v>
+        <v>0.8908</v>
       </c>
       <c r="N21" t="n">
-        <v>119</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2334</v>
+        <v>0.5157</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.215</v>
+        <v>-0.065</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5745</v>
+        <v>1.2692</v>
       </c>
       <c r="N22" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4289</v>
+        <v>1.081</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1743</v>
+        <v>0.4392</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.273</v>
+        <v>-0.15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4289</v>
+        <v>1.081</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6356000000000001</v>
+        <v>1.081</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2067</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6356000000000001</v>
+        <v>1.081</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5152</v>
+        <v>1.081</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2067</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3085</v>
+        <v>1.081</v>
       </c>
       <c r="N23" t="n">
-        <v>218</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3677</v>
+        <v>0.9506</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1494</v>
+        <v>0.3863</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2974</v>
+        <v>-0.2089</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3677</v>
+        <v>0.9506</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3677</v>
+        <v>0.9506</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3677</v>
+        <v>0.9506</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3708</v>
+        <v>0.9897</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3708</v>
+        <v>0.9897</v>
       </c>
       <c r="N24" t="n">
         <v>170</v>
@@ -1550,323 +1550,323 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3492</v>
+        <v>0.8154</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1419</v>
+        <v>0.3313</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3048</v>
+        <v>-0.2699</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3492</v>
+        <v>0.8154</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3012</v>
+        <v>0.8154</v>
       </c>
       <c r="G25" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3012</v>
+        <v>0.8154</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2441</v>
+        <v>0.8154</v>
       </c>
       <c r="J25" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2921</v>
+        <v>0.8154</v>
       </c>
       <c r="N25" t="n">
-        <v>256</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3377</v>
+        <v>0.8084</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1372</v>
+        <v>0.3285</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3094</v>
+        <v>-0.2731</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3377</v>
+        <v>0.8084</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.8151</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0862</v>
+        <v>-0.0067</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.8151</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6067</v>
+        <v>0.4238</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0862</v>
+        <v>-0.0067</v>
       </c>
       <c r="K26" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L26" t="n">
-        <v>185</v>
+        <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4795</v>
+        <v>0.4171</v>
       </c>
       <c r="N26" t="n">
-        <v>232</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1262</v>
+        <v>0.3272</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3202</v>
+        <v>-0.2745</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3106</v>
+        <v>0.8053</v>
       </c>
       <c r="N27" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1195</v>
+        <v>0.2198</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3268</v>
+        <v>-0.3938</v>
       </c>
       <c r="E28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="F28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="I28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.294</v>
+        <v>0.541</v>
       </c>
       <c r="N28" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1983</v>
+        <v>0.3436</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0806</v>
+        <v>0.1396</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3649</v>
+        <v>-0.4829</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1983</v>
+        <v>0.3436</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4182</v>
+        <v>0.3436</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2199</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4182</v>
+        <v>0.3436</v>
       </c>
       <c r="I29" t="n">
-        <v>0.339</v>
+        <v>0.3577</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2199</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="L29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1191</v>
+        <v>0.3577</v>
       </c>
       <c r="N29" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0799</v>
+        <v>0.1786</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0325</v>
+        <v>0.0726</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4757</v>
+        <v>-0.5574</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0799</v>
+        <v>0.1786</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2656</v>
+        <v>-0.892</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1857</v>
+        <v>1.0706</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2656</v>
+        <v>-0.892</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2153</v>
+        <v>-0.4638</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1857</v>
+        <v>1.0706</v>
       </c>
       <c r="K30" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L30" t="n">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.02959999999999999</v>
+        <v>0.6068</v>
       </c>
       <c r="N30" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2504</v>
+        <v>0.1013</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1017</v>
+        <v>0.0412</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5437</v>
+        <v>-0.5923</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2504</v>
+        <v>0.1013</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2504</v>
+        <v>-0.1831</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.2844</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2504</v>
+        <v>-0.1831</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2525</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2844</v>
       </c>
       <c r="K31" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2525</v>
+        <v>0.1892</v>
       </c>
       <c r="N31" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1098</v>
+        <v>0.0254</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5516</v>
+        <v>-0.6098</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2703</v>
+        <v>0.0626</v>
       </c>
       <c r="N32" t="n">
         <v>68</v>
@@ -1918,124 +1918,124 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.206</v>
+        <v>0.015</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6459</v>
+        <v>-0.6213</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5069</v>
+        <v>0.037</v>
       </c>
       <c r="N33" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2275</v>
+        <v>-0.0885</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6669</v>
+        <v>-0.7363</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5598</v>
+        <v>-0.2178</v>
       </c>
       <c r="N34" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2444</v>
+        <v>-0.1123</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6836</v>
+        <v>-0.7627</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6016</v>
+        <v>-0.2763</v>
       </c>
       <c r="N35" t="n">
         <v>96</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3362</v>
+        <v>-0.2909</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7735</v>
+        <v>-0.9613</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8274</v>
+        <v>-0.716</v>
       </c>
       <c r="N36" t="n">
         <v>96</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4476</v>
+        <v>-0.305</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8827</v>
+        <v>-0.9769</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1015</v>
+        <v>-0.7506</v>
       </c>
       <c r="N37" t="n">
         <v>96</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.488</v>
+        <v>-1.0851</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6046</v>
+        <v>-0.4409</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0367</v>
+        <v>-1.1279</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.488</v>
+        <v>-1.0851</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8968</v>
+        <v>-1.0851</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8968</v>
+        <v>-1.0851</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7269</v>
+        <v>-1.0851</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L38" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3181</v>
+        <v>-1.0851</v>
       </c>
       <c r="N38" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5617</v>
+        <v>-1.1726</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.4765</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0661</v>
+        <v>-1.1674</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5617</v>
+        <v>-1.1726</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5617</v>
+        <v>-0.8012</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.3714</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5617</v>
+        <v>-0.8012</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5617</v>
+        <v>-0.4166</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.3714</v>
       </c>
       <c r="K39" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5617</v>
+        <v>-0.788</v>
       </c>
       <c r="N39" t="n">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6422</v>
+        <v>-0.5321</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0736</v>
+        <v>-1.2292</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5805</v>
+        <v>-1.3095</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6612</v>
+        <v>-1.5615</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.675</v>
+        <v>-0.6345</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1057</v>
+        <v>-1.343</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6612</v>
+        <v>-1.5615</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6807</v>
+        <v>-0.9257</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9805</v>
+        <v>-0.6358</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.6807</v>
+        <v>-0.9257</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5517</v>
+        <v>-0.4813</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9805</v>
+        <v>-0.6358</v>
       </c>
       <c r="K41" t="n">
         <v>58</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5322</v>
+        <v>-1.1171</v>
       </c>
       <c r="N41" t="n">
         <v>113</v>
@@ -2429,10 +2429,10 @@
         <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6634</v>
+        <v>0.5826</v>
       </c>
       <c r="J2" t="n">
-        <v>17.9118</v>
+        <v>15.7302</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5413</v>
+        <v>0.4682</v>
       </c>
       <c r="J3" t="n">
-        <v>14.6151</v>
+        <v>12.6414</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1356</v>
+        <v>-0.0635</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.6612</v>
+        <v>-1.7145</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1559</v>
+        <v>-0.0769</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.2093</v>
+        <v>-2.0763</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1935</v>
+        <v>-0.1022</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.2245</v>
+        <v>-2.7594</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4819</v>
+        <v>0.4358</v>
       </c>
       <c r="J7" t="n">
-        <v>13.0113</v>
+        <v>11.7666</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0398</v>
+        <v>0.0473</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0746</v>
+        <v>1.2771</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0229</v>
+        <v>-0.0027</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6183</v>
+        <v>-0.07290000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0842</v>
+        <v>-0.0393</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2734</v>
+        <v>-1.0611</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2385</v>
+        <v>-0.1382</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.4395</v>
+        <v>-3.7314</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3382</v>
+        <v>0.3716</v>
       </c>
       <c r="J12" t="n">
-        <v>12.1752</v>
+        <v>13.3776</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1485</v>
+        <v>0.1356</v>
       </c>
       <c r="J13" t="n">
-        <v>5.346</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.612</v>
+        <v>-6.0552</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3919</v>
+        <v>-0.2492</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.1084</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4065</v>
+        <v>-0.2591</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.634</v>
+        <v>-9.3276</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0963</v>
+        <v>1.0554</v>
       </c>
       <c r="J17" t="n">
-        <v>39.4668</v>
+        <v>37.9944</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8338</v>
+        <v>0.8172</v>
       </c>
       <c r="J18" t="n">
-        <v>30.0168</v>
+        <v>29.4192</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6666</v>
+        <v>0.6493</v>
       </c>
       <c r="J19" t="n">
-        <v>23.9976</v>
+        <v>23.3748</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3645</v>
+        <v>-0.2947</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.122</v>
+        <v>-10.6092</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8275</v>
+        <v>-0.784</v>
       </c>
       <c r="J21" t="n">
-        <v>-29.79</v>
+        <v>-28.224</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>22.338</v>
+        <v>27.162</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.571</v>
+        <v>0.6877</v>
       </c>
       <c r="J23" t="n">
-        <v>20.556</v>
+        <v>24.7572</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.169</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.084</v>
+        <v>-3.3228</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.319</v>
+        <v>-0.1925</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.484</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5653</v>
+        <v>-0.3688</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.3508</v>
+        <v>-13.2768</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8595</v>
+        <v>0.8243</v>
       </c>
       <c r="J27" t="n">
-        <v>30.942</v>
+        <v>29.6748</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5105</v>
+        <v>0.4612</v>
       </c>
       <c r="J28" t="n">
-        <v>18.378</v>
+        <v>16.6032</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3353</v>
+        <v>-0.2902</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.0708</v>
+        <v>-10.4472</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4259</v>
+        <v>-0.3775</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.3324</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.77</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6984</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.6904</v>
+        <v>-25.1424</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.492</v>
+        <v>0.4024</v>
       </c>
       <c r="J32" t="n">
-        <v>13.776</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4385</v>
+        <v>0.3717</v>
       </c>
       <c r="J33" t="n">
-        <v>12.278</v>
+        <v>10.4076</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2088</v>
+        <v>0.1905</v>
       </c>
       <c r="J34" t="n">
-        <v>5.8464</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2345</v>
+        <v>-0.1324</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.566</v>
+        <v>-3.7072</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3291</v>
+        <v>-0.1975</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.2148</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1099</v>
+        <v>0.0709</v>
       </c>
       <c r="J37" t="n">
-        <v>3.0772</v>
+        <v>1.9852</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0867</v>
+        <v>0.0522</v>
       </c>
       <c r="J38" t="n">
-        <v>2.4276</v>
+        <v>1.4616</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0867</v>
+        <v>0.0522</v>
       </c>
       <c r="J39" t="n">
-        <v>2.4276</v>
+        <v>1.4616</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0921</v>
+        <v>-0.0601</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.5788</v>
+        <v>-1.6828</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4032</v>
+        <v>-0.2544</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.2896</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.5356</v>
       </c>
       <c r="J42" t="n">
-        <v>20.883</v>
+        <v>16.068</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5689</v>
+        <v>0.4629</v>
       </c>
       <c r="J43" t="n">
-        <v>17.067</v>
+        <v>13.887</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4283</v>
+        <v>0.3879</v>
       </c>
       <c r="J44" t="n">
-        <v>12.849</v>
+        <v>11.637</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3969</v>
+        <v>0.3726</v>
       </c>
       <c r="J45" t="n">
-        <v>11.907</v>
+        <v>11.178</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4771</v>
+        <v>-0.4109</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.313</v>
+        <v>-12.327</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3658</v>
+        <v>0.38</v>
       </c>
       <c r="J47" t="n">
-        <v>10.974</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.14</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3051</v>
+        <v>0.3316</v>
       </c>
       <c r="J48" t="n">
-        <v>9.153</v>
+        <v>9.948</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1202</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.606</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.507</v>
+        <v>-3.921</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5532</v>
+        <v>-0.3609</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.596</v>
+        <v>-10.827</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.23</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6641</v>
+        <v>0.5191</v>
       </c>
       <c r="J52" t="n">
-        <v>18.5948</v>
+        <v>14.5348</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6389</v>
+        <v>0.5047</v>
       </c>
       <c r="J53" t="n">
-        <v>17.8892</v>
+        <v>14.1316</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2467</v>
+        <v>0.29</v>
       </c>
       <c r="J54" t="n">
-        <v>6.9076</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.06</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1505</v>
+        <v>0.2011</v>
       </c>
       <c r="J55" t="n">
-        <v>4.214</v>
+        <v>5.6308</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1171</v>
+        <v>0.1695</v>
       </c>
       <c r="J56" t="n">
-        <v>3.2788</v>
+        <v>4.746</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.19</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3861</v>
+        <v>0.3945</v>
       </c>
       <c r="J57" t="n">
-        <v>10.8108</v>
+        <v>11.046</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1936</v>
+        <v>0.1957</v>
       </c>
       <c r="J58" t="n">
-        <v>5.4208</v>
+        <v>5.4796</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1086</v>
+        <v>-0.0718</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.0408</v>
+        <v>-2.0104</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3263</v>
+        <v>-0.203</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.1364</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4842</v>
+        <v>-0.3116</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.5576</v>
+        <v>-8.7248</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1026</v>
+        <v>0.065</v>
       </c>
       <c r="J62" t="n">
-        <v>2.1546</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.91</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0951</v>
+        <v>-0.0961</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.9971</v>
+        <v>-2.0181</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.74</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.401</v>
+        <v>-0.2701</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.420999999999999</v>
+        <v>-5.6721</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5487</v>
+        <v>-0.3646</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.5227</v>
+        <v>-7.6566</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.0981</v>
+        <v>-8.051399999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.6392</v>
+        <v>1.1533</v>
       </c>
       <c r="J67" t="n">
-        <v>34.4232</v>
+        <v>24.2193</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.75</v>
       </c>
       <c r="I68" t="n">
-        <v>1.586</v>
+        <v>1.1187</v>
       </c>
       <c r="J68" t="n">
-        <v>33.306</v>
+        <v>23.4927</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.36</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7667</v>
+        <v>0.656</v>
       </c>
       <c r="J69" t="n">
-        <v>16.1007</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.19</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3791</v>
+        <v>0.4237</v>
       </c>
       <c r="J70" t="n">
-        <v>7.9611</v>
+        <v>8.8977</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.13</v>
       </c>
       <c r="I71" t="n">
-        <v>0.231</v>
+        <v>0.328</v>
       </c>
       <c r="J71" t="n">
-        <v>4.851</v>
+        <v>6.888</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5867</v>
+        <v>0.5545</v>
       </c>
       <c r="J72" t="n">
-        <v>19.9478</v>
+        <v>18.853</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3288</v>
+        <v>0.3579</v>
       </c>
       <c r="J73" t="n">
-        <v>11.1792</v>
+        <v>12.1686</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1263</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.2942</v>
+        <v>-2.2508</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2856</v>
+        <v>-0.1703</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.7104</v>
+        <v>-5.7902</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4044</v>
+        <v>-0.2524</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.7496</v>
+        <v>-8.5816</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.41</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0944</v>
+        <v>0.7786</v>
       </c>
       <c r="J77" t="n">
-        <v>37.2096</v>
+        <v>26.4724</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.41</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0944</v>
+        <v>0.7786</v>
       </c>
       <c r="J78" t="n">
-        <v>37.2096</v>
+        <v>26.4724</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.24</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7126</v>
+        <v>0.5413</v>
       </c>
       <c r="J79" t="n">
-        <v>24.2284</v>
+        <v>18.4042</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7476</v>
+        <v>-0.6986</v>
       </c>
       <c r="J80" t="n">
-        <v>-25.4184</v>
+        <v>-23.7524</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1233</v>
+        <v>-1.1144</v>
       </c>
       <c r="J81" t="n">
-        <v>-38.1922</v>
+        <v>-37.8896</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.88</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7676</v>
+        <v>1.5181</v>
       </c>
       <c r="J82" t="n">
-        <v>35.352</v>
+        <v>30.362</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2463</v>
+        <v>1.2033</v>
       </c>
       <c r="J83" t="n">
-        <v>24.926</v>
+        <v>24.066</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.59</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2249</v>
+        <v>1.192</v>
       </c>
       <c r="J84" t="n">
-        <v>24.498</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.42</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8469</v>
+        <v>0.9794</v>
       </c>
       <c r="J85" t="n">
-        <v>16.938</v>
+        <v>19.588</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.31</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6152</v>
+        <v>0.747</v>
       </c>
       <c r="J86" t="n">
-        <v>12.304</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.78</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2163</v>
+        <v>-0.193</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.326</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2936</v>
+        <v>-0.2471</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.872</v>
+        <v>-4.942</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4876</v>
+        <v>-0.365</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.752000000000001</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7337</v>
+        <v>-0.5024</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.674</v>
+        <v>-10.048</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.41</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.018</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3527</v>
+        <v>0.295</v>
       </c>
       <c r="J92" t="n">
-        <v>8.817500000000001</v>
+        <v>7.375</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2147</v>
+        <v>-0.1609</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.3675</v>
+        <v>-4.0225</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2589</v>
+        <v>-0.1807</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.4725</v>
+        <v>-4.5175</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4551</v>
+        <v>-0.2973</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.3775</v>
+        <v>-7.4325</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5521</v>
+        <v>-0.3638</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.8025</v>
+        <v>-9.095000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7285</v>
+        <v>0.6562</v>
       </c>
       <c r="J97" t="n">
-        <v>18.2125</v>
+        <v>16.405</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5496</v>
+        <v>0.4964</v>
       </c>
       <c r="J98" t="n">
-        <v>13.74</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.37</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4639</v>
       </c>
       <c r="J99" t="n">
-        <v>12.765</v>
+        <v>11.5975</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.259</v>
+        <v>0.2711</v>
       </c>
       <c r="J100" t="n">
-        <v>6.475</v>
+        <v>6.7775</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0062</v>
+        <v>0.0464</v>
       </c>
       <c r="J101" t="n">
-        <v>0.155</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.31</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8445</v>
+        <v>0.8329</v>
       </c>
       <c r="J102" t="n">
-        <v>21.957</v>
+        <v>21.6554</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.751</v>
+        <v>0.7387</v>
       </c>
       <c r="J103" t="n">
-        <v>19.526</v>
+        <v>19.2062</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6016</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>15.6416</v>
+        <v>15.4518</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1075</v>
+        <v>0.1651</v>
       </c>
       <c r="J105" t="n">
-        <v>2.795</v>
+        <v>4.2926</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4597</v>
+        <v>-0.3902</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.9522</v>
+        <v>-10.1452</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4365</v>
+        <v>0.5079</v>
       </c>
       <c r="J107" t="n">
-        <v>11.349</v>
+        <v>13.2054</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1096</v>
+        <v>0.1143</v>
       </c>
       <c r="J108" t="n">
-        <v>2.8496</v>
+        <v>2.9718</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0619</v>
+        <v>0.0646</v>
       </c>
       <c r="J109" t="n">
-        <v>1.6094</v>
+        <v>1.6796</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2478</v>
+        <v>-0.1464</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.4428</v>
+        <v>-3.8064</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.86</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2961</v>
+        <v>-0.1786</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.6986</v>
+        <v>-4.6436</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.672</v>
+        <v>1.4396</v>
       </c>
       <c r="J112" t="n">
-        <v>43.472</v>
+        <v>37.4296</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7139</v>
+        <v>0.7369</v>
       </c>
       <c r="J113" t="n">
-        <v>18.5614</v>
+        <v>19.1594</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2435</v>
+        <v>0.3197</v>
       </c>
       <c r="J114" t="n">
-        <v>6.331</v>
+        <v>8.312200000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1576</v>
+        <v>0.2338</v>
       </c>
       <c r="J115" t="n">
-        <v>4.0976</v>
+        <v>6.0788</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0051</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.1086</v>
+        <v>-0.1326</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1975</v>
+        <v>0.1985</v>
       </c>
       <c r="J117" t="n">
-        <v>5.135</v>
+        <v>5.161</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.179</v>
+        <v>0.1762</v>
       </c>
       <c r="J118" t="n">
-        <v>4.654</v>
+        <v>4.5812</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2063</v>
+        <v>-0.128</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.3638</v>
+        <v>-3.328</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2753</v>
+        <v>-0.1707</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1578</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3386</v>
+        <v>-0.2119</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.803599999999999</v>
+        <v>-5.5094</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8669</v>
+        <v>0.8653</v>
       </c>
       <c r="J122" t="n">
-        <v>23.4063</v>
+        <v>23.3631</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7502</v>
+        <v>0.75</v>
       </c>
       <c r="J123" t="n">
-        <v>20.2554</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5412</v>
+        <v>0.5614</v>
       </c>
       <c r="J124" t="n">
-        <v>14.6124</v>
+        <v>15.1578</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.13</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3276</v>
+        <v>0.3869</v>
       </c>
       <c r="J125" t="n">
-        <v>8.8452</v>
+        <v>10.4463</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0609</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.6443</v>
+        <v>0.2376</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2538</v>
+        <v>0.266</v>
       </c>
       <c r="J127" t="n">
-        <v>6.8526</v>
+        <v>7.182</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0038</v>
+        <v>-0.0145</v>
       </c>
       <c r="J128" t="n">
-        <v>0.1026</v>
+        <v>-0.3915</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0905</v>
+        <v>-0.0704</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.4435</v>
+        <v>-1.9008</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.32</v>
+        <v>-0.2006</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.640000000000001</v>
+        <v>-5.4162</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3807</v>
+        <v>-0.2408</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.2789</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.86</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.131</v>
+        <v>-0.1286</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.882</v>
+        <v>-2.8292</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3563</v>
+        <v>-0.2761</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.8386</v>
+        <v>-6.0742</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4536</v>
+        <v>-0.3215</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.979200000000001</v>
+        <v>-7.073</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.61</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5522</v>
+        <v>-0.3763</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.1484</v>
+        <v>-8.278600000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.53</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6657</v>
+        <v>-0.451</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.6454</v>
+        <v>-9.922000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.11</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0593</v>
+        <v>1.8018</v>
       </c>
       <c r="J137" t="n">
-        <v>45.3046</v>
+        <v>39.6396</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0844</v>
+        <v>1.088</v>
       </c>
       <c r="J138" t="n">
-        <v>23.8568</v>
+        <v>23.936</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.499</v>
+        <v>0.6099</v>
       </c>
       <c r="J139" t="n">
-        <v>10.978</v>
+        <v>13.4178</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.22</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4525</v>
+        <v>0.5618</v>
       </c>
       <c r="J140" t="n">
-        <v>9.955</v>
+        <v>12.3596</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.11</v>
       </c>
       <c r="I141" t="n">
-        <v>0.181</v>
+        <v>0.2775</v>
       </c>
       <c r="J141" t="n">
-        <v>3.982</v>
+        <v>6.105</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3914</v>
+        <v>0.3304</v>
       </c>
       <c r="J142" t="n">
-        <v>10.9592</v>
+        <v>9.251200000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3178</v>
+        <v>0.2675</v>
       </c>
       <c r="J143" t="n">
-        <v>8.898400000000001</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1355</v>
+        <v>0.1343</v>
       </c>
       <c r="J144" t="n">
-        <v>3.794</v>
+        <v>3.7604</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0968</v>
+        <v>0.1044</v>
       </c>
       <c r="J145" t="n">
-        <v>2.7104</v>
+        <v>2.9232</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.148</v>
+        <v>-0.0736</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.144</v>
+        <v>-2.0608</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.627</v>
+        <v>0.5835</v>
       </c>
       <c r="J147" t="n">
-        <v>17.556</v>
+        <v>16.338</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4052</v>
+        <v>0.3587</v>
       </c>
       <c r="J148" t="n">
-        <v>11.3456</v>
+        <v>10.0436</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.88</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.267</v>
+        <v>-0.1584</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.476</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3592</v>
+        <v>-0.2212</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.0576</v>
+        <v>-6.1936</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4023</v>
+        <v>-0.2513</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.2644</v>
+        <v>-7.0364</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5491</v>
+        <v>0.6611</v>
       </c>
       <c r="J152" t="n">
-        <v>12.0802</v>
+        <v>14.5442</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2684</v>
+        <v>-0.2102</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.9048</v>
+        <v>-4.6244</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.6</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5948</v>
+        <v>-0.3978</v>
       </c>
       <c r="J154" t="n">
-        <v>-13.0856</v>
+        <v>-8.7516</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6217</v>
+        <v>-0.4166</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.6774</v>
+        <v>-9.1652</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6742</v>
+        <v>-0.4539</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.8324</v>
+        <v>-9.985799999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5259</v>
+        <v>1.3485</v>
       </c>
       <c r="J157" t="n">
-        <v>33.5698</v>
+        <v>29.667</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1186</v>
+        <v>1.0961</v>
       </c>
       <c r="J158" t="n">
-        <v>24.6092</v>
+        <v>24.1142</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0119</v>
+        <v>1.0328</v>
       </c>
       <c r="J159" t="n">
-        <v>22.2618</v>
+        <v>22.7216</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.2</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4271</v>
+        <v>0.5265</v>
       </c>
       <c r="J160" t="n">
-        <v>9.3962</v>
+        <v>11.583</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0761</v>
+        <v>0.0074</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.6742</v>
+        <v>0.1628</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6727</v>
+        <v>0.856</v>
       </c>
       <c r="J162" t="n">
-        <v>14.1267</v>
+        <v>17.976</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.86</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.138</v>
+        <v>-0.1326</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.898</v>
+        <v>-2.7846</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.52</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.6835</v>
+        <v>-0.4627</v>
       </c>
       <c r="J164" t="n">
-        <v>-14.3535</v>
+        <v>-9.716699999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.41</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.8238</v>
+        <v>-0.5657</v>
       </c>
       <c r="J165" t="n">
-        <v>-17.2998</v>
+        <v>-11.8797</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8965</v>
+        <v>-0.6217</v>
       </c>
       <c r="J166" t="n">
-        <v>-18.8265</v>
+        <v>-13.0557</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.75</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5777</v>
+        <v>1.3888</v>
       </c>
       <c r="J167" t="n">
-        <v>33.1317</v>
+        <v>29.1648</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.63</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3545</v>
+        <v>1.2497</v>
       </c>
       <c r="J168" t="n">
-        <v>28.4445</v>
+        <v>26.2437</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8462</v>
+        <v>0.9584</v>
       </c>
       <c r="J169" t="n">
-        <v>17.7702</v>
+        <v>20.1264</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.8983</v>
       </c>
       <c r="J170" t="n">
-        <v>16.3737</v>
+        <v>18.8643</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.16</v>
       </c>
       <c r="I171" t="n">
-        <v>0.3008</v>
+        <v>0.4058</v>
       </c>
       <c r="J171" t="n">
-        <v>6.3168</v>
+        <v>8.521800000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.89</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1275</v>
+        <v>-0.1181</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.805</v>
+        <v>-2.5982</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1448</v>
+        <v>-0.1294</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.1856</v>
+        <v>-2.8468</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2469</v>
+        <v>-0.1934</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.4318</v>
+        <v>-4.2548</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4604</v>
+        <v>-0.3071</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.1288</v>
+        <v>-6.7562</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6145</v>
+        <v>-0.4105</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.519</v>
+        <v>-9.031000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2157</v>
+        <v>1.1502</v>
       </c>
       <c r="J177" t="n">
-        <v>26.7454</v>
+        <v>25.3044</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0295</v>
+        <v>1.0375</v>
       </c>
       <c r="J178" t="n">
-        <v>22.649</v>
+        <v>22.825</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.38</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8952</v>
+        <v>0.9369</v>
       </c>
       <c r="J179" t="n">
-        <v>19.6944</v>
+        <v>20.6118</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3651</v>
+        <v>0.4582</v>
       </c>
       <c r="J180" t="n">
-        <v>8.0322</v>
+        <v>10.0804</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3651</v>
+        <v>0.4582</v>
       </c>
       <c r="J181" t="n">
-        <v>8.0322</v>
+        <v>10.0804</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.45</v>
+        <v>1.2878</v>
       </c>
       <c r="J182" t="n">
-        <v>49.3</v>
+        <v>43.7852</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6834</v>
+        <v>0.6583</v>
       </c>
       <c r="J183" t="n">
-        <v>23.2356</v>
+        <v>22.3822</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2742</v>
+        <v>0.2961</v>
       </c>
       <c r="J184" t="n">
-        <v>9.322800000000001</v>
+        <v>10.0674</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4697</v>
+        <v>-0.4055</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.9698</v>
+        <v>-13.787</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9546</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>-32.4564</v>
+        <v>-31.4466</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.231</v>
+        <v>0.2484</v>
       </c>
       <c r="J187" t="n">
-        <v>7.854</v>
+        <v>8.445600000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0634</v>
+        <v>-0.0354</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.1556</v>
+        <v>-1.2036</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0634</v>
+        <v>-0.0354</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.1556</v>
+        <v>-1.2036</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.488</v>
+        <v>-2.5534</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J191" t="n">
-        <v>-4.488</v>
+        <v>-2.5534</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J192" t="n">
-        <v>6.507</v>
+        <v>7.1307</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1308</v>
+        <v>0.1374</v>
       </c>
       <c r="J193" t="n">
-        <v>3.5316</v>
+        <v>3.7098</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="J194" t="n">
-        <v>2.3463</v>
+        <v>2.4354</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.159</v>
+        <v>-0.0892</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.293</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.92</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1961</v>
+        <v>-0.1127</v>
       </c>
       <c r="J196" t="n">
-        <v>-5.2947</v>
+        <v>-3.0429</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6626</v>
+        <v>0.6176</v>
       </c>
       <c r="J197" t="n">
-        <v>17.8902</v>
+        <v>16.6752</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6117</v>
+        <v>0.5653</v>
       </c>
       <c r="J198" t="n">
-        <v>16.5159</v>
+        <v>15.2631</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5858</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>15.8166</v>
+        <v>14.5476</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1669</v>
+        <v>-0.1319</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5063</v>
+        <v>-3.5613</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.2904</v>
+        <v>-1.3053</v>
       </c>
       <c r="J201" t="n">
-        <v>-34.8408</v>
+        <v>-35.2431</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.34</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9025</v>
+        <v>0.896</v>
       </c>
       <c r="J202" t="n">
-        <v>21.66</v>
+        <v>21.504</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5621</v>
+        <v>0.5658</v>
       </c>
       <c r="J203" t="n">
-        <v>13.4904</v>
+        <v>13.5792</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4029</v>
+        <v>0.4436</v>
       </c>
       <c r="J204" t="n">
-        <v>9.669600000000001</v>
+        <v>10.6464</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2544</v>
+        <v>0.3103</v>
       </c>
       <c r="J205" t="n">
-        <v>6.1056</v>
+        <v>7.4472</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0648</v>
+        <v>0.1277</v>
       </c>
       <c r="J206" t="n">
-        <v>1.5552</v>
+        <v>3.0648</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3984</v>
+        <v>0.4532</v>
       </c>
       <c r="J207" t="n">
-        <v>9.5616</v>
+        <v>10.8768</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1726</v>
+        <v>0.1718</v>
       </c>
       <c r="J208" t="n">
-        <v>4.1424</v>
+        <v>4.1232</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1533</v>
+        <v>0.1489</v>
       </c>
       <c r="J209" t="n">
-        <v>3.6792</v>
+        <v>3.5736</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4164</v>
+        <v>-0.2638</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.993600000000001</v>
+        <v>-6.3312</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.71</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4989</v>
+        <v>-0.3219</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.9736</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.07</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2352</v>
+        <v>0.2329</v>
       </c>
       <c r="J212" t="n">
-        <v>5.6448</v>
+        <v>5.5896</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.198</v>
+        <v>0.1859</v>
       </c>
       <c r="J213" t="n">
-        <v>4.752</v>
+        <v>4.4616</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.04</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1783</v>
+        <v>0.1612</v>
       </c>
       <c r="J214" t="n">
-        <v>4.2792</v>
+        <v>3.8688</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4987</v>
+        <v>-0.3265</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.9688</v>
+        <v>-7.836</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.38</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8829</v>
+        <v>-0.6118</v>
       </c>
       <c r="J216" t="n">
-        <v>-21.1896</v>
+        <v>-14.6832</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6401</v>
+        <v>1.4203</v>
       </c>
       <c r="J217" t="n">
-        <v>39.3624</v>
+        <v>34.0872</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9786</v>
       </c>
       <c r="J218" t="n">
-        <v>22.8984</v>
+        <v>23.4864</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.33</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7879</v>
+        <v>0.8353</v>
       </c>
       <c r="J219" t="n">
-        <v>18.9096</v>
+        <v>20.0472</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.32</v>
       </c>
       <c r="I220" t="n">
-        <v>0.76</v>
+        <v>0.8139</v>
       </c>
       <c r="J220" t="n">
-        <v>18.24</v>
+        <v>19.5336</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.801</v>
+        <v>-0.7516</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.224</v>
+        <v>-18.0384</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.92</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.4996</v>
+        <v>-1.7986</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0832</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.9136</v>
+        <v>-2.0769</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2527</v>
+        <v>-0.2004</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.8121</v>
+        <v>-4.6092</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5681</v>
+        <v>-0.3794</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.0663</v>
+        <v>-8.7262</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.52</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7003</v>
+        <v>-0.4728</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.1069</v>
+        <v>-10.8744</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4073</v>
+        <v>1.2742</v>
       </c>
       <c r="J227" t="n">
-        <v>32.3679</v>
+        <v>29.3066</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3116</v>
+        <v>1.2146</v>
       </c>
       <c r="J228" t="n">
-        <v>30.1668</v>
+        <v>27.9358</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.32</v>
       </c>
       <c r="I229" t="n">
-        <v>0.703</v>
+        <v>0.8033</v>
       </c>
       <c r="J229" t="n">
-        <v>16.169</v>
+        <v>18.4759</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.27</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5867</v>
+        <v>0.6902</v>
       </c>
       <c r="J230" t="n">
-        <v>13.4941</v>
+        <v>15.8746</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.11</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1943</v>
+        <v>0.2878</v>
       </c>
       <c r="J231" t="n">
-        <v>4.4689</v>
+        <v>6.6194</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4877</v>
+        <v>1.3141</v>
       </c>
       <c r="J232" t="n">
-        <v>37.1925</v>
+        <v>32.8525</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3098</v>
+        <v>0.364</v>
       </c>
       <c r="J233" t="n">
-        <v>7.745</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1908</v>
+        <v>0.2515</v>
       </c>
       <c r="J234" t="n">
-        <v>4.77</v>
+        <v>6.2875</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1284</v>
+        <v>0.191</v>
       </c>
       <c r="J235" t="n">
-        <v>3.21</v>
+        <v>4.775</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2509</v>
+        <v>-0.1749</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.2725</v>
+        <v>-4.3725</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9594</v>
+        <v>1.1414</v>
       </c>
       <c r="J237" t="n">
-        <v>23.985</v>
+        <v>28.535</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5407</v>
+        <v>0.6434</v>
       </c>
       <c r="J238" t="n">
-        <v>13.5175</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.65</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.5805</v>
+        <v>-0.3807</v>
       </c>
       <c r="J239" t="n">
-        <v>-14.5125</v>
+        <v>-9.5175</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5931</v>
+        <v>-0.39</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.8275</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.62</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.618</v>
+        <v>-0.4085</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.45</v>
+        <v>-10.2125</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2763/event_2763_evp_summary.xlsx
+++ b/database/event/2763/event_2763_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2732</v>
+        <v>6.2145</v>
       </c>
       <c r="C2" t="n">
-        <v>2.549</v>
+        <v>2.5251</v>
       </c>
       <c r="D2" t="n">
-        <v>2.194</v>
+        <v>2.2048</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2732</v>
+        <v>6.2145</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7087</v>
+        <v>2.6479</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5645</v>
+        <v>3.5666</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0575</v>
+        <v>3.8423</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1097</v>
+        <v>2.0748</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5645</v>
+        <v>3.5666</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>185</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6742</v>
+        <v>5.641400000000001</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0448</v>
+        <v>5.0867</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0498</v>
+        <v>2.0669</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6395</v>
+        <v>1.6914</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0448</v>
+        <v>5.0867</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6736</v>
+        <v>2.6307</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3712</v>
+        <v>2.456</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9336</v>
+        <v>3.7856</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0453</v>
+        <v>2.0442</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3712</v>
+        <v>2.456</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>154</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4165</v>
+        <v>4.5002</v>
       </c>
       <c r="N3" t="n">
         <v>256</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9785</v>
+        <v>3.9865</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6166</v>
+        <v>1.6198</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1581</v>
+        <v>1.1905</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9785</v>
+        <v>3.9865</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8454</v>
+        <v>2.7756</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1331</v>
+        <v>1.2109</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5392</v>
+        <v>4.2636</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3602</v>
+        <v>2.3023</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1331</v>
+        <v>1.2109</v>
       </c>
       <c r="K4" t="n">
         <v>102</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4933</v>
+        <v>3.5132</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7796</v>
+        <v>3.757</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5358</v>
+        <v>1.5266</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0683</v>
+        <v>1.0861</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7796</v>
+        <v>3.757</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9529</v>
+        <v>2.865</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8267</v>
+        <v>0.892</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9179</v>
+        <v>4.5586</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5571</v>
+        <v>2.4616</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8267</v>
+        <v>0.892</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3838</v>
+        <v>3.3536</v>
       </c>
       <c r="N5" t="n">
         <v>218</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4509</v>
+        <v>3.3843</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4022</v>
+        <v>1.3751</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9164</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4509</v>
+        <v>3.3843</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4399</v>
+        <v>2.3502</v>
       </c>
       <c r="G6" t="n">
-        <v>1.011</v>
+        <v>1.0341</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1103</v>
+        <v>2.8599</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6172</v>
+        <v>1.5443</v>
       </c>
       <c r="J6" t="n">
-        <v>1.011</v>
+        <v>1.0341</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>185</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6282</v>
+        <v>2.5784</v>
       </c>
       <c r="N6" t="n">
         <v>232</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3252</v>
+        <v>3.3219</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3511</v>
+        <v>1.3498</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8631</v>
+        <v>0.888</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3252</v>
+        <v>3.3219</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7543</v>
+        <v>2.6712</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5709</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2181</v>
+        <v>3.9191</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1932</v>
+        <v>2.1163</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5709</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>47</v>
@@ -759,7 +759,7 @@
         <v>185</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7641</v>
+        <v>2.767</v>
       </c>
       <c r="N7" t="n">
         <v>232</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0864</v>
+        <v>3.0698</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2541</v>
+        <v>1.2473</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7553</v>
+        <v>0.7732</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0864</v>
+        <v>3.0698</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0864</v>
+        <v>1.5624</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.5074</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4175</v>
+        <v>1.5624</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5581</v>
+        <v>0.8437</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.5074</v>
       </c>
       <c r="K8" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5581</v>
+        <v>2.3511</v>
       </c>
       <c r="N8" t="n">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0375</v>
+        <v>2.8795</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2342</v>
+        <v>1.17</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7333</v>
+        <v>0.6866</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0375</v>
+        <v>2.8795</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6876</v>
+        <v>2.8332</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3499</v>
+        <v>0.0463</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6876</v>
+        <v>4.4536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8774999999999999</v>
+        <v>2.4049</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3499</v>
+        <v>0.0463</v>
       </c>
       <c r="K9" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2274</v>
+        <v>2.4512</v>
       </c>
       <c r="N9" t="n">
-        <v>256</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9798</v>
+        <v>2.7874</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2108</v>
+        <v>1.1326</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9798</v>
+        <v>2.7874</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9171</v>
+        <v>2.7874</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7916</v>
+        <v>3.3759</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4914</v>
+        <v>3.4629</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="L10" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5541</v>
+        <v>3.4629</v>
       </c>
       <c r="N10" t="n">
-        <v>218</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6829</v>
+        <v>2.4683</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0901</v>
+        <v>1.0029</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5732</v>
+        <v>0.4994</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6829</v>
+        <v>2.4683</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6829</v>
+        <v>2.4683</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6829</v>
+        <v>2.6773</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7932</v>
+        <v>2.7463</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7932</v>
+        <v>2.7463</v>
       </c>
       <c r="N11" t="n">
         <v>170</v>
@@ -952,415 +952,415 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4828</v>
+        <v>2.3651</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0088</v>
+        <v>0.961</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4828</v>
+        <v>0.4524</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4828</v>
+        <v>2.3651</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7492</v>
+        <v>1.9539</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2664</v>
+        <v>0.4112</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>1.9539</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1838</v>
+        <v>1.0551</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2664</v>
+        <v>0.4112</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9174</v>
+        <v>1.4663</v>
       </c>
       <c r="N12" t="n">
-        <v>113</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2536</v>
+        <v>2.362</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9157</v>
+        <v>0.9597</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3794</v>
+        <v>0.451</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2536</v>
+        <v>2.362</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2536</v>
+        <v>2.6595</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.2975</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2536</v>
+        <v>3.8806</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2536</v>
+        <v>2.0955</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.2975</v>
       </c>
       <c r="K13" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2536</v>
+        <v>1.798</v>
       </c>
       <c r="N13" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2241</v>
+        <v>2.1687</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8812</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3661</v>
+        <v>0.363</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2241</v>
+        <v>2.1687</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2253</v>
+        <v>2.1687</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3542</v>
+        <v>2.1687</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2241</v>
+        <v>2.1687</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2229</v>
+        <v>2.1687</v>
       </c>
       <c r="N14" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2035</v>
+        <v>2.1163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8953</v>
+        <v>0.8599</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3568</v>
+        <v>0.3392</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2035</v>
+        <v>2.1163</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9875</v>
+        <v>2.1438</v>
       </c>
       <c r="G15" t="n">
-        <v>0.216</v>
+        <v>-0.0275</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9875</v>
+        <v>2.1791</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0334</v>
+        <v>1.1767</v>
       </c>
       <c r="J15" t="n">
-        <v>0.216</v>
+        <v>-0.0275</v>
       </c>
       <c r="K15" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L15" t="n">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2494</v>
+        <v>1.1492</v>
       </c>
       <c r="N15" t="n">
-        <v>256</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9395</v>
+        <v>1.8996</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7881</v>
+        <v>0.7719</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2376</v>
+        <v>0.2405</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9395</v>
+        <v>1.8996</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4512</v>
+        <v>2.6332</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5117</v>
+        <v>-0.7336</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1503</v>
+        <v>3.7936</v>
       </c>
       <c r="I16" t="n">
-        <v>1.638</v>
+        <v>2.0485</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5117</v>
+        <v>-0.7336</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="L16" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1263</v>
+        <v>1.3149</v>
       </c>
       <c r="N16" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9156</v>
+        <v>1.8495</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7784</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2268</v>
+        <v>0.2177</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9156</v>
+        <v>1.8495</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9156</v>
+        <v>2.3811</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.5316</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9156</v>
+        <v>2.9619</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9156</v>
+        <v>1.5994</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.5316</v>
       </c>
       <c r="K17" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9156</v>
+        <v>1.0678</v>
       </c>
       <c r="N17" t="n">
-        <v>119</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9012</v>
+        <v>1.7909</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7725</v>
+        <v>0.7277</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2203</v>
+        <v>0.1911</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9012</v>
+        <v>1.7909</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7086</v>
+        <v>1.7909</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8074</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0571</v>
+        <v>1.7909</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1095</v>
+        <v>1.7909</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8074</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="L18" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3021</v>
+        <v>1.7909</v>
       </c>
       <c r="N18" t="n">
-        <v>232</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.765</v>
+        <v>1.6492</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6701</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1588</v>
+        <v>0.1265</v>
       </c>
       <c r="E19" t="n">
-        <v>1.765</v>
+        <v>1.6492</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7596</v>
+        <v>1.6492</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0054</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7596</v>
+        <v>1.6492</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9149</v>
+        <v>1.6917</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0054</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9203</v>
+        <v>1.6917</v>
       </c>
       <c r="N19" t="n">
-        <v>218</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6242</v>
+        <v>1.5154</v>
       </c>
       <c r="C20" t="n">
-        <v>0.66</v>
+        <v>0.6157</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6242</v>
+        <v>1.5154</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6242</v>
+        <v>1.5319</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6242</v>
+        <v>1.5319</v>
       </c>
       <c r="I20" t="n">
-        <v>1.691</v>
+        <v>0.8272</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="K20" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>1.691</v>
+        <v>0.8107000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>170</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4155</v>
+        <v>1.3936</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5752</v>
+        <v>0.5663</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001</v>
+        <v>0.0102</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4155</v>
+        <v>1.3936</v>
       </c>
       <c r="F21" t="n">
-        <v>1.093</v>
+        <v>0.9896</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3225</v>
+        <v>0.404</v>
       </c>
       <c r="H21" t="n">
-        <v>1.093</v>
+        <v>0.9896</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5683</v>
+        <v>0.5344</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3225</v>
+        <v>0.404</v>
       </c>
       <c r="K21" t="n">
         <v>102</v>
@@ -1403,7 +1403,7 @@
         <v>154</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8908</v>
+        <v>0.9384</v>
       </c>
       <c r="N21" t="n">
         <v>256</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5157</v>
+        <v>0.4951</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.065</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2692</v>
+        <v>1.2185</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4392</v>
+        <v>0.4053</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.15</v>
+        <v>-0.1701</v>
       </c>
       <c r="E23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.081</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>119</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9506</v>
+        <v>0.9109</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3863</v>
+        <v>0.3701</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2089</v>
+        <v>-0.2095</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9506</v>
+        <v>0.9109</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9506</v>
+        <v>0.9109</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9506</v>
+        <v>0.9109</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9897</v>
+        <v>0.9344</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9897</v>
+        <v>0.9344</v>
       </c>
       <c r="N24" t="n">
         <v>170</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8154</v>
+        <v>0.8153</v>
       </c>
       <c r="C25" t="n">
         <v>0.3313</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2699</v>
+        <v>-0.2531</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8154</v>
+        <v>0.8153</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8154</v>
+        <v>0.8198</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8154</v>
+        <v>0.8198</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8154</v>
+        <v>0.4427</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8154</v>
+        <v>0.4382</v>
       </c>
       <c r="N25" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8084</v>
+        <v>0.745</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3285</v>
+        <v>0.3027</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2731</v>
+        <v>-0.2851</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8084</v>
+        <v>0.745</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8151</v>
+        <v>0.745</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0067</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8151</v>
+        <v>0.745</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4238</v>
+        <v>0.745</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0067</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4171</v>
+        <v>0.745</v>
       </c>
       <c r="N26" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3272</v>
+        <v>0.3015</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2745</v>
+        <v>-0.2864</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8053</v>
+        <v>0.742</v>
       </c>
       <c r="N27" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2198</v>
+        <v>0.1914</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3938</v>
+        <v>-0.4098</v>
       </c>
       <c r="E28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="F28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="I28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.541</v>
+        <v>0.471</v>
       </c>
       <c r="N28" t="n">
         <v>96</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3436</v>
+        <v>0.4149</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1396</v>
+        <v>0.1686</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4829</v>
+        <v>-0.4353</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3436</v>
+        <v>0.4149</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3436</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.1231</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3436</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3577</v>
+        <v>-0.3824</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.1231</v>
       </c>
       <c r="K29" t="n">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3577</v>
+        <v>0.7406999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1786</v>
+        <v>0.3649</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0726</v>
+        <v>0.1483</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5574</v>
+        <v>-0.4581</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1786</v>
+        <v>0.3649</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.892</v>
+        <v>0.3649</v>
       </c>
       <c r="G30" t="n">
-        <v>1.0706</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.892</v>
+        <v>0.3649</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4638</v>
+        <v>0.3743</v>
       </c>
       <c r="J30" t="n">
-        <v>1.0706</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="L30" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6068</v>
+        <v>0.3743</v>
       </c>
       <c r="N30" t="n">
-        <v>232</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1013</v>
+        <v>0.1962</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0412</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5923</v>
+        <v>-0.5349</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1013</v>
+        <v>0.1962</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1831</v>
+        <v>-0.1335</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2844</v>
+        <v>0.3297</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1831</v>
+        <v>-0.1335</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2844</v>
+        <v>0.3297</v>
       </c>
       <c r="K31" t="n">
         <v>58</v>
@@ -1863,7 +1863,7 @@
         <v>55</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1892</v>
+        <v>0.2576</v>
       </c>
       <c r="N31" t="n">
         <v>113</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0254</v>
+        <v>0.0028</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6098</v>
+        <v>-0.6211</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0626</v>
+        <v>0.0069</v>
       </c>
       <c r="N32" t="n">
         <v>68</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="C33" t="n">
-        <v>0.015</v>
+        <v>-0.0249</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6213</v>
+        <v>-0.6521</v>
       </c>
       <c r="E33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="F33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="I33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.037</v>
+        <v>-0.0612</v>
       </c>
       <c r="N33" t="n">
         <v>68</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0885</v>
+        <v>-0.0993</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7363</v>
+        <v>-0.7355</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2444</v>
       </c>
       <c r="N34" t="n">
         <v>96</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1123</v>
+        <v>-0.1179</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7627</v>
+        <v>-0.7563</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2763</v>
+        <v>-0.2901</v>
       </c>
       <c r="N35" t="n">
         <v>96</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2909</v>
+        <v>-0.306</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9613</v>
+        <v>-0.967</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.716</v>
+        <v>-0.753</v>
       </c>
       <c r="N36" t="n">
         <v>96</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.305</v>
+        <v>-0.3171</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9769</v>
+        <v>-0.9795</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7506</v>
+        <v>-0.7805</v>
       </c>
       <c r="N37" t="n">
         <v>96</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0851</v>
+        <v>-1.0381</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4409</v>
+        <v>-0.4218</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1279</v>
+        <v>-1.0968</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0851</v>
+        <v>-1.0381</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0851</v>
+        <v>-0.6476</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0851</v>
+        <v>-0.6476</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0851</v>
+        <v>-0.3497</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="K38" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0851</v>
+        <v>-0.7402</v>
       </c>
       <c r="N38" t="n">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1726</v>
+        <v>-1.1203</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4765</v>
+        <v>-0.4552</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1674</v>
+        <v>-1.1342</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1726</v>
+        <v>-1.1203</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8012</v>
+        <v>-1.1203</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.3714</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8012</v>
+        <v>-1.1203</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4166</v>
+        <v>-1.1203</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.3714</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L39" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.788</v>
+        <v>-1.1203</v>
       </c>
       <c r="N39" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5321</v>
+        <v>-0.5442</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2292</v>
+        <v>-1.2339</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3095</v>
+        <v>-1.3393</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5615</v>
+        <v>-1.4243</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6345</v>
+        <v>-0.5787</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.343</v>
+        <v>-1.2726</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5615</v>
+        <v>-1.4243</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9257</v>
+        <v>-0.7613</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6358</v>
+        <v>-0.663</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9257</v>
+        <v>-0.7613</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4813</v>
+        <v>-0.4111</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6358</v>
+        <v>-0.663</v>
       </c>
       <c r="K41" t="n">
         <v>58</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1171</v>
+        <v>-1.0741</v>
       </c>
       <c r="N41" t="n">
         <v>113</v>
@@ -2429,10 +2429,10 @@
         <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5826</v>
+        <v>0.5845</v>
       </c>
       <c r="J2" t="n">
-        <v>15.7302</v>
+        <v>15.7815</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4682</v>
+        <v>0.4768</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6414</v>
+        <v>12.8736</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0635</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7145</v>
+        <v>-1.8522</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0769</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.0763</v>
+        <v>-2.2437</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1022</v>
+        <v>-0.1099</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7594</v>
+        <v>-2.9673</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4358</v>
+        <v>0.4357</v>
       </c>
       <c r="J7" t="n">
-        <v>11.7666</v>
+        <v>11.7639</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0473</v>
+        <v>0.0551</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2771</v>
+        <v>1.4877</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0027</v>
+        <v>-0.002</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0393</v>
+        <v>-0.0452</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0611</v>
+        <v>-1.2204</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1382</v>
+        <v>-0.15</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7314</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="J12" t="n">
-        <v>13.3776</v>
+        <v>13.1652</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1356</v>
+        <v>0.1387</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8816</v>
+        <v>4.9932</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.0552</v>
+        <v>-6.6168</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2492</v>
+        <v>-0.2645</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.9712</v>
+        <v>-9.522</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2591</v>
+        <v>-0.2742</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.3276</v>
+        <v>-9.8712</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0554</v>
+        <v>1.0098</v>
       </c>
       <c r="J17" t="n">
-        <v>37.9944</v>
+        <v>36.3528</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8172</v>
+        <v>0.7694</v>
       </c>
       <c r="J18" t="n">
-        <v>29.4192</v>
+        <v>27.6984</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6493</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>23.3748</v>
+        <v>22.374</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2947</v>
+        <v>-0.2836</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.6092</v>
+        <v>-10.2096</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.784</v>
+        <v>-0.7248</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.224</v>
+        <v>-26.0928</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.724</v>
       </c>
       <c r="J22" t="n">
-        <v>27.162</v>
+        <v>26.064</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6877</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>24.7572</v>
+        <v>23.8968</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1022</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.3228</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1925</v>
+        <v>-0.205</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.93</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3688</v>
+        <v>-0.3784</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.2768</v>
+        <v>-13.6224</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8243</v>
+        <v>0.766</v>
       </c>
       <c r="J27" t="n">
-        <v>29.6748</v>
+        <v>27.576</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4612</v>
+        <v>0.4443</v>
       </c>
       <c r="J28" t="n">
-        <v>16.6032</v>
+        <v>15.9948</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2902</v>
+        <v>-0.2877</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.4472</v>
+        <v>-10.3572</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3775</v>
+        <v>-0.3682</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.59</v>
+        <v>-13.2552</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.77</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6984</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.1424</v>
+        <v>-23.6052</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4024</v>
+        <v>0.4465</v>
       </c>
       <c r="J32" t="n">
-        <v>11.2672</v>
+        <v>12.502</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3717</v>
+        <v>0.4022</v>
       </c>
       <c r="J33" t="n">
-        <v>10.4076</v>
+        <v>11.2616</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1905</v>
+        <v>0.203</v>
       </c>
       <c r="J34" t="n">
-        <v>5.334</v>
+        <v>5.684</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1324</v>
+        <v>-0.1427</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.7072</v>
+        <v>-3.9956</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1975</v>
+        <v>-0.209</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.53</v>
+        <v>-5.852</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0709</v>
+        <v>0.0784</v>
       </c>
       <c r="J37" t="n">
-        <v>1.9852</v>
+        <v>2.1952</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0522</v>
+        <v>0.0584</v>
       </c>
       <c r="J38" t="n">
-        <v>1.4616</v>
+        <v>1.6352</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0522</v>
+        <v>0.0584</v>
       </c>
       <c r="J39" t="n">
-        <v>1.4616</v>
+        <v>1.6352</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0601</v>
+        <v>-0.0702</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6828</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2544</v>
+        <v>-0.2686</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.1232</v>
+        <v>-7.5208</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5356</v>
+        <v>0.5911</v>
       </c>
       <c r="J42" t="n">
-        <v>16.068</v>
+        <v>17.733</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4629</v>
+        <v>0.5097</v>
       </c>
       <c r="J43" t="n">
-        <v>13.887</v>
+        <v>15.291</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3879</v>
+        <v>0.4187</v>
       </c>
       <c r="J44" t="n">
-        <v>11.637</v>
+        <v>12.561</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3726</v>
+        <v>0.3958</v>
       </c>
       <c r="J45" t="n">
-        <v>11.178</v>
+        <v>11.874</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4109</v>
+        <v>-0.3915</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.327</v>
+        <v>-11.745</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.38</v>
+        <v>0.4066</v>
       </c>
       <c r="J47" t="n">
-        <v>11.4</v>
+        <v>12.198</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.14</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3316</v>
+        <v>0.335</v>
       </c>
       <c r="J48" t="n">
-        <v>9.948</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0838</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.187</v>
+        <v>-2.514</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.921</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3609</v>
+        <v>-0.3722</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.827</v>
+        <v>-11.166</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.23</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5191</v>
+        <v>0.5732</v>
       </c>
       <c r="J52" t="n">
-        <v>14.5348</v>
+        <v>16.0496</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5047</v>
+        <v>0.5571</v>
       </c>
       <c r="J53" t="n">
-        <v>14.1316</v>
+        <v>15.5988</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.29</v>
+        <v>0.2949</v>
       </c>
       <c r="J54" t="n">
-        <v>8.119999999999999</v>
+        <v>8.257199999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.06</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2011</v>
+        <v>0.2114</v>
       </c>
       <c r="J55" t="n">
-        <v>5.6308</v>
+        <v>5.9192</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1695</v>
+        <v>0.1814</v>
       </c>
       <c r="J56" t="n">
-        <v>4.746</v>
+        <v>5.0792</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.19</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3945</v>
+        <v>0.427</v>
       </c>
       <c r="J57" t="n">
-        <v>11.046</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1957</v>
+        <v>0.2003</v>
       </c>
       <c r="J58" t="n">
-        <v>5.4796</v>
+        <v>5.6084</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0718</v>
+        <v>-0.0829</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.0104</v>
+        <v>-2.3212</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.203</v>
+        <v>-0.2178</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.684</v>
+        <v>-6.0984</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3116</v>
+        <v>-0.3247</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.7248</v>
+        <v>-9.0916</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.065</v>
+        <v>0.0473</v>
       </c>
       <c r="J62" t="n">
-        <v>1.365</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.91</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0961</v>
+        <v>-0.1147</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.0181</v>
+        <v>-2.4087</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.74</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2701</v>
+        <v>-0.2887</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.6721</v>
+        <v>-6.0627</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3646</v>
+        <v>-0.3801</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.6566</v>
+        <v>-7.9821</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3834</v>
+        <v>-0.398</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.051399999999999</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1533</v>
+        <v>1.2708</v>
       </c>
       <c r="J67" t="n">
-        <v>24.2193</v>
+        <v>26.6868</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.75</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1187</v>
+        <v>1.2342</v>
       </c>
       <c r="J68" t="n">
-        <v>23.4927</v>
+        <v>25.9182</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.36</v>
       </c>
       <c r="I69" t="n">
-        <v>0.656</v>
+        <v>0.7343</v>
       </c>
       <c r="J69" t="n">
-        <v>13.776</v>
+        <v>15.4203</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.19</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4237</v>
+        <v>0.4759</v>
       </c>
       <c r="J70" t="n">
-        <v>8.8977</v>
+        <v>9.9939</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.13</v>
       </c>
       <c r="I71" t="n">
-        <v>0.328</v>
+        <v>0.3482</v>
       </c>
       <c r="J71" t="n">
-        <v>6.888</v>
+        <v>7.3122</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5545</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>18.853</v>
+        <v>21.0256</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3579</v>
+        <v>0.3756</v>
       </c>
       <c r="J73" t="n">
-        <v>12.1686</v>
+        <v>12.7704</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.2508</v>
+        <v>-2.5432</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1703</v>
+        <v>-0.1828</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.7902</v>
+        <v>-6.2152</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2524</v>
+        <v>-0.265</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.5816</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.41</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7786</v>
+        <v>0.8554</v>
       </c>
       <c r="J77" t="n">
-        <v>26.4724</v>
+        <v>29.0836</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.41</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7786</v>
+        <v>0.8554</v>
       </c>
       <c r="J78" t="n">
-        <v>26.4724</v>
+        <v>29.0836</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.24</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5413</v>
+        <v>0.596</v>
       </c>
       <c r="J79" t="n">
-        <v>18.4042</v>
+        <v>20.264</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6986</v>
+        <v>-0.6513</v>
       </c>
       <c r="J80" t="n">
-        <v>-23.7524</v>
+        <v>-22.1442</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1144</v>
+        <v>-1.0132</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.8896</v>
+        <v>-34.4488</v>
       </c>
     </row>
     <row r="82">
@@ -5669,10 +5669,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2033</v>
+        <v>1.1827</v>
       </c>
       <c r="J83" t="n">
-        <v>24.066</v>
+        <v>23.654</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.59</v>
       </c>
       <c r="I84" t="n">
-        <v>1.192</v>
+        <v>1.1705</v>
       </c>
       <c r="J84" t="n">
-        <v>23.84</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.42</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9794</v>
+        <v>0.9347</v>
       </c>
       <c r="J85" t="n">
-        <v>19.588</v>
+        <v>18.694</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.31</v>
       </c>
       <c r="I86" t="n">
-        <v>0.747</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>14.94</v>
+        <v>14.506</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.78</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.193</v>
+        <v>-0.2209</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.86</v>
+        <v>-4.418</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2471</v>
+        <v>-0.2729</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.942</v>
+        <v>-5.458</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.365</v>
+        <v>-0.3855</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.3</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5024</v>
+        <v>-0.515</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.048</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.41</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.55</v>
+        <v>-0.5592</v>
       </c>
       <c r="J91" t="n">
-        <v>-11</v>
+        <v>-11.184</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.295</v>
+        <v>0.2913</v>
       </c>
       <c r="J92" t="n">
-        <v>7.375</v>
+        <v>7.2825</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1609</v>
+        <v>-0.1782</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.0225</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1807</v>
+        <v>-0.1983</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.5175</v>
+        <v>-4.9575</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2973</v>
+        <v>-0.3136</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.4325</v>
+        <v>-7.84</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3638</v>
+        <v>-0.3778</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.095000000000001</v>
+        <v>-9.445</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6562</v>
+        <v>0.659</v>
       </c>
       <c r="J97" t="n">
-        <v>16.405</v>
+        <v>16.475</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4964</v>
+        <v>0.5088</v>
       </c>
       <c r="J98" t="n">
-        <v>12.41</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.37</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4639</v>
+        <v>0.4779</v>
       </c>
       <c r="J99" t="n">
-        <v>11.5975</v>
+        <v>11.9475</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2711</v>
+        <v>0.2912</v>
       </c>
       <c r="J100" t="n">
-        <v>6.7775</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0464</v>
+        <v>0.0653</v>
       </c>
       <c r="J101" t="n">
-        <v>1.16</v>
+        <v>1.6325</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.31</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8329</v>
+        <v>0.7845</v>
       </c>
       <c r="J102" t="n">
-        <v>21.6554</v>
+        <v>20.397</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7387</v>
+        <v>0.7019</v>
       </c>
       <c r="J103" t="n">
-        <v>19.2062</v>
+        <v>18.2494</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="J104" t="n">
-        <v>15.4518</v>
+        <v>14.9162</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1651</v>
+        <v>0.1784</v>
       </c>
       <c r="J105" t="n">
-        <v>4.2926</v>
+        <v>4.6384</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3902</v>
+        <v>-0.3708</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.1452</v>
+        <v>-9.6408</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5079</v>
+        <v>0.4982</v>
       </c>
       <c r="J107" t="n">
-        <v>13.2054</v>
+        <v>12.9532</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1143</v>
+        <v>0.1233</v>
       </c>
       <c r="J108" t="n">
-        <v>2.9718</v>
+        <v>3.2058</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0646</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>1.6796</v>
+        <v>1.8824</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1464</v>
+        <v>-0.1591</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.8064</v>
+        <v>-4.1366</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.86</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1786</v>
+        <v>-0.1918</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.6436</v>
+        <v>-4.9868</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4396</v>
+        <v>1.4232</v>
       </c>
       <c r="J112" t="n">
-        <v>37.4296</v>
+        <v>37.0032</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7369</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>19.1594</v>
+        <v>18.3326</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3197</v>
+        <v>0.3286</v>
       </c>
       <c r="J114" t="n">
-        <v>8.312200000000001</v>
+        <v>8.5436</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2338</v>
+        <v>0.249</v>
       </c>
       <c r="J115" t="n">
-        <v>6.0788</v>
+        <v>6.474</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0051</v>
+        <v>0.0183</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.1326</v>
+        <v>0.4758</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1985</v>
+        <v>0.2024</v>
       </c>
       <c r="J117" t="n">
-        <v>5.161</v>
+        <v>5.2624</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1762</v>
+        <v>0.1806</v>
       </c>
       <c r="J118" t="n">
-        <v>4.5812</v>
+        <v>4.6956</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.128</v>
+        <v>-0.1421</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.328</v>
+        <v>-3.6946</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1707</v>
+        <v>-0.1857</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.4382</v>
+        <v>-4.8282</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2119</v>
+        <v>-0.227</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.5094</v>
+        <v>-5.902</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8653</v>
+        <v>0.8153</v>
       </c>
       <c r="J122" t="n">
-        <v>23.3631</v>
+        <v>22.0131</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.75</v>
+        <v>0.7141</v>
       </c>
       <c r="J123" t="n">
-        <v>20.25</v>
+        <v>19.2807</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5614</v>
+        <v>0.546</v>
       </c>
       <c r="J124" t="n">
-        <v>15.1578</v>
+        <v>14.742</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.13</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3869</v>
+        <v>0.3873</v>
       </c>
       <c r="J125" t="n">
-        <v>10.4463</v>
+        <v>10.4571</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="J126" t="n">
-        <v>0.2376</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.266</v>
+        <v>0.2668</v>
       </c>
       <c r="J127" t="n">
-        <v>7.182</v>
+        <v>7.2036</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0145</v>
+        <v>-0.0206</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.3915</v>
+        <v>-0.5562</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0704</v>
+        <v>-0.0819</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.9008</v>
+        <v>-2.2113</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2006</v>
+        <v>-0.2159</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.4162</v>
+        <v>-5.8293</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2408</v>
+        <v>-0.2559</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.5016</v>
+        <v>-6.9093</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.86</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1286</v>
+        <v>-0.1531</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.8292</v>
+        <v>-3.3682</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2761</v>
+        <v>-0.2973</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.0742</v>
+        <v>-6.5406</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3215</v>
+        <v>-0.3415</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.073</v>
+        <v>-7.513</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.61</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3763</v>
+        <v>-0.3941</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.278600000000001</v>
+        <v>-8.670199999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.53</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.451</v>
+        <v>-0.4648</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.922000000000001</v>
+        <v>-10.2256</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.11</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8018</v>
+        <v>1.8102</v>
       </c>
       <c r="J137" t="n">
-        <v>39.6396</v>
+        <v>39.8244</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.088</v>
+        <v>1.0541</v>
       </c>
       <c r="J138" t="n">
-        <v>23.936</v>
+        <v>23.1902</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6099</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>13.4178</v>
+        <v>13.1846</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.22</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5618</v>
+        <v>0.5564</v>
       </c>
       <c r="J140" t="n">
-        <v>12.3596</v>
+        <v>12.2408</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.11</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2775</v>
+        <v>0.2991</v>
       </c>
       <c r="J141" t="n">
-        <v>6.105</v>
+        <v>6.5802</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3304</v>
+        <v>0.3439</v>
       </c>
       <c r="J142" t="n">
-        <v>9.251200000000001</v>
+        <v>9.629200000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2675</v>
+        <v>0.2827</v>
       </c>
       <c r="J143" t="n">
-        <v>7.49</v>
+        <v>7.9156</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1343</v>
+        <v>0.1492</v>
       </c>
       <c r="J144" t="n">
-        <v>3.7604</v>
+        <v>4.1776</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1044</v>
+        <v>0.1184</v>
       </c>
       <c r="J145" t="n">
-        <v>2.9232</v>
+        <v>3.3152</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0736</v>
+        <v>-0.0806</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.0608</v>
+        <v>-2.2568</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5835</v>
+        <v>0.5717</v>
       </c>
       <c r="J147" t="n">
-        <v>16.338</v>
+        <v>16.0076</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3587</v>
+        <v>0.3625</v>
       </c>
       <c r="J148" t="n">
-        <v>10.0436</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.88</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1584</v>
+        <v>-0.1711</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.4352</v>
+        <v>-4.7908</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2212</v>
+        <v>-0.2342</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.1936</v>
+        <v>-6.5576</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2513</v>
+        <v>-0.2641</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.0364</v>
+        <v>-7.3948</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6611</v>
+        <v>0.6148</v>
       </c>
       <c r="J152" t="n">
-        <v>14.5442</v>
+        <v>13.5256</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2102</v>
+        <v>-0.2302</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.6244</v>
+        <v>-5.0644</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.6</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3978</v>
+        <v>-0.4125</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.7516</v>
+        <v>-9.074999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4166</v>
+        <v>-0.4303</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.1652</v>
+        <v>-9.4666</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4539</v>
+        <v>-0.4656</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.985799999999999</v>
+        <v>-10.2432</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3485</v>
+        <v>1.3323</v>
       </c>
       <c r="J157" t="n">
-        <v>29.667</v>
+        <v>29.3106</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0961</v>
+        <v>1.0615</v>
       </c>
       <c r="J158" t="n">
-        <v>24.1142</v>
+        <v>23.353</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0328</v>
+        <v>0.9873</v>
       </c>
       <c r="J159" t="n">
-        <v>22.7216</v>
+        <v>21.7206</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.2</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5265</v>
+        <v>0.5221</v>
       </c>
       <c r="J160" t="n">
-        <v>11.583</v>
+        <v>11.4862</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0074</v>
+        <v>0.0397</v>
       </c>
       <c r="J161" t="n">
-        <v>0.1628</v>
+        <v>0.8734</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.856</v>
+        <v>0.7806</v>
       </c>
       <c r="J162" t="n">
-        <v>17.976</v>
+        <v>16.3926</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.86</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1326</v>
+        <v>-0.1562</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.7846</v>
+        <v>-3.2802</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.52</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4627</v>
+        <v>-0.4754</v>
       </c>
       <c r="J164" t="n">
-        <v>-9.716699999999999</v>
+        <v>-9.9834</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.41</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5657</v>
+        <v>-0.5715</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.8797</v>
+        <v>-12.0015</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6217</v>
+        <v>-0.6233</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.0557</v>
+        <v>-13.0893</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.75</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3888</v>
+        <v>1.3782</v>
       </c>
       <c r="J167" t="n">
-        <v>29.1648</v>
+        <v>28.9422</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.63</v>
       </c>
       <c r="I168" t="n">
-        <v>1.2497</v>
+        <v>1.2301</v>
       </c>
       <c r="J168" t="n">
-        <v>26.2437</v>
+        <v>25.8321</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9584</v>
+        <v>0.9105</v>
       </c>
       <c r="J169" t="n">
-        <v>20.1264</v>
+        <v>19.1205</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8983</v>
+        <v>0.8548</v>
       </c>
       <c r="J170" t="n">
-        <v>18.8643</v>
+        <v>17.9508</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.16</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4058</v>
+        <v>0.4173</v>
       </c>
       <c r="J171" t="n">
-        <v>8.521800000000001</v>
+        <v>8.763299999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.89</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1181</v>
+        <v>-0.1374</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.5982</v>
+        <v>-3.0228</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1294</v>
+        <v>-0.1488</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.8468</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1934</v>
+        <v>-0.2128</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.2548</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3071</v>
+        <v>-0.3249</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.7562</v>
+        <v>-7.1478</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4105</v>
+        <v>-0.424</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.031000000000001</v>
+        <v>-9.327999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1502</v>
+        <v>1.1193</v>
       </c>
       <c r="J177" t="n">
-        <v>25.3044</v>
+        <v>24.6246</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0375</v>
+        <v>0.9917</v>
       </c>
       <c r="J178" t="n">
-        <v>22.825</v>
+        <v>21.8174</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.38</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9369</v>
+        <v>0.8863</v>
       </c>
       <c r="J179" t="n">
-        <v>20.6118</v>
+        <v>19.4986</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4582</v>
+        <v>0.4592</v>
       </c>
       <c r="J180" t="n">
-        <v>10.0804</v>
+        <v>10.1024</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4582</v>
+        <v>0.4592</v>
       </c>
       <c r="J181" t="n">
-        <v>10.0804</v>
+        <v>10.1024</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2878</v>
+        <v>1.2547</v>
       </c>
       <c r="J182" t="n">
-        <v>43.7852</v>
+        <v>42.6598</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6583</v>
+        <v>0.6277</v>
       </c>
       <c r="J183" t="n">
-        <v>22.3822</v>
+        <v>21.3418</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2961</v>
+        <v>0.299</v>
       </c>
       <c r="J184" t="n">
-        <v>10.0674</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4055</v>
+        <v>-0.3877</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.787</v>
+        <v>-13.1818</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.8491</v>
       </c>
       <c r="J186" t="n">
-        <v>-31.4466</v>
+        <v>-28.8694</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2484</v>
+        <v>0.254</v>
       </c>
       <c r="J187" t="n">
-        <v>8.445600000000001</v>
+        <v>8.635999999999999</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0354</v>
+        <v>-0.0422</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.2036</v>
+        <v>-1.4348</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0354</v>
+        <v>-0.0422</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.2036</v>
+        <v>-1.4348</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.5534</v>
+        <v>-2.907</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.5534</v>
+        <v>-2.907</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J192" t="n">
-        <v>7.1307</v>
+        <v>7.2927</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1374</v>
+        <v>0.1465</v>
       </c>
       <c r="J193" t="n">
-        <v>3.7098</v>
+        <v>3.9555</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0902</v>
+        <v>0.0988</v>
       </c>
       <c r="J194" t="n">
-        <v>2.4354</v>
+        <v>2.6676</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0892</v>
+        <v>-0.0998</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.4084</v>
+        <v>-2.6946</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.92</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1127</v>
+        <v>-0.1245</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.0429</v>
+        <v>-3.3615</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6176</v>
+        <v>0.5849</v>
       </c>
       <c r="J197" t="n">
-        <v>16.6752</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5653</v>
+        <v>0.5384</v>
       </c>
       <c r="J198" t="n">
-        <v>15.2631</v>
+        <v>14.5368</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5148</v>
       </c>
       <c r="J199" t="n">
-        <v>14.5476</v>
+        <v>13.8996</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1319</v>
+        <v>-0.1367</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.5613</v>
+        <v>-3.6909</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.3053</v>
+        <v>-1.179</v>
       </c>
       <c r="J201" t="n">
-        <v>-35.2431</v>
+        <v>-31.833</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.34</v>
       </c>
       <c r="I202" t="n">
-        <v>0.896</v>
+        <v>0.8408</v>
       </c>
       <c r="J202" t="n">
-        <v>21.504</v>
+        <v>20.1792</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5658</v>
+        <v>0.549</v>
       </c>
       <c r="J203" t="n">
-        <v>13.5792</v>
+        <v>13.176</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4436</v>
+        <v>0.438</v>
       </c>
       <c r="J204" t="n">
-        <v>10.6464</v>
+        <v>10.512</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3103</v>
+        <v>0.3156</v>
       </c>
       <c r="J205" t="n">
-        <v>7.4472</v>
+        <v>7.5744</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1277</v>
+        <v>0.1437</v>
       </c>
       <c r="J206" t="n">
-        <v>3.0648</v>
+        <v>3.4488</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4532</v>
+        <v>0.4443</v>
       </c>
       <c r="J207" t="n">
-        <v>10.8768</v>
+        <v>10.6632</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1718</v>
+        <v>0.1774</v>
       </c>
       <c r="J208" t="n">
-        <v>4.1232</v>
+        <v>4.2576</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1489</v>
+        <v>0.1548</v>
       </c>
       <c r="J209" t="n">
-        <v>3.5736</v>
+        <v>3.7152</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2638</v>
+        <v>-0.2779</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.3312</v>
+        <v>-6.6696</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.71</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3219</v>
+        <v>-0.3346</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.7256</v>
+        <v>-8.0304</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.07</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2329</v>
+        <v>0.2276</v>
       </c>
       <c r="J212" t="n">
-        <v>5.5896</v>
+        <v>5.4624</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1859</v>
+        <v>0.1818</v>
       </c>
       <c r="J213" t="n">
-        <v>4.4616</v>
+        <v>4.3632</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.04</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1612</v>
+        <v>0.1575</v>
       </c>
       <c r="J214" t="n">
-        <v>3.8688</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3265</v>
+        <v>-0.3418</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.836</v>
+        <v>-8.203200000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4203</v>
+        <v>1.4061</v>
       </c>
       <c r="J217" t="n">
-        <v>34.0872</v>
+        <v>33.7464</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9786</v>
+        <v>0.9263</v>
       </c>
       <c r="J218" t="n">
-        <v>23.4864</v>
+        <v>22.2312</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.33</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8353</v>
+        <v>0.7947</v>
       </c>
       <c r="J219" t="n">
-        <v>20.0472</v>
+        <v>19.0728</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.32</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8139</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J220" t="n">
-        <v>19.5336</v>
+        <v>18.6168</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7516</v>
+        <v>-0.6887</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.0384</v>
+        <v>-16.5288</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.92</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0978</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.7986</v>
+        <v>-2.2494</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.1102</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.0769</v>
+        <v>-2.5346</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2004</v>
+        <v>-0.2205</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.6092</v>
+        <v>-5.0715</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3794</v>
+        <v>-0.3949</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.7262</v>
+        <v>-9.082700000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.52</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4728</v>
+        <v>-0.4833</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.8744</v>
+        <v>-11.1159</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2742</v>
+        <v>1.2538</v>
       </c>
       <c r="J227" t="n">
-        <v>29.3066</v>
+        <v>28.8374</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2146</v>
+        <v>1.19</v>
       </c>
       <c r="J228" t="n">
-        <v>27.9358</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.32</v>
       </c>
       <c r="I229" t="n">
-        <v>0.8033</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>18.4759</v>
+        <v>17.6778</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.27</v>
       </c>
       <c r="I230" t="n">
-        <v>0.6902</v>
+        <v>0.6687</v>
       </c>
       <c r="J230" t="n">
-        <v>15.8746</v>
+        <v>15.3801</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.11</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2878</v>
+        <v>0.3063</v>
       </c>
       <c r="J231" t="n">
-        <v>6.6194</v>
+        <v>7.0449</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3141</v>
+        <v>1.2869</v>
       </c>
       <c r="J232" t="n">
-        <v>32.8525</v>
+        <v>32.1725</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.364</v>
+        <v>0.3654</v>
       </c>
       <c r="J233" t="n">
-        <v>9.1</v>
+        <v>9.135</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2515</v>
+        <v>0.2613</v>
       </c>
       <c r="J234" t="n">
-        <v>6.2875</v>
+        <v>6.5325</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.191</v>
+        <v>0.2044</v>
       </c>
       <c r="J235" t="n">
-        <v>4.775</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1749</v>
+        <v>-0.1665</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.3725</v>
+        <v>-4.1625</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1414</v>
+        <v>1.111</v>
       </c>
       <c r="J237" t="n">
-        <v>28.535</v>
+        <v>27.775</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6434</v>
+        <v>0.6197</v>
       </c>
       <c r="J238" t="n">
-        <v>16.085</v>
+        <v>15.4925</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.65</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3807</v>
+        <v>-0.3911</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.5175</v>
+        <v>-9.7775</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.75</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.62</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4085</v>
+        <v>-0.4178</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.2125</v>
+        <v>-10.445</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2763/event_2763_evp_summary.xlsx
+++ b/database/event/2763/event_2763_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2145</v>
+        <v>6.1833</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5251</v>
+        <v>2.5124</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2048</v>
+        <v>2.211</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2145</v>
+        <v>6.1833</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6479</v>
+        <v>2.7017</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5666</v>
+        <v>3.4816</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8423</v>
+        <v>3.7007</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0748</v>
+        <v>2.0778</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5666</v>
+        <v>3.4816</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>185</v>
       </c>
       <c r="M2" t="n">
-        <v>5.641400000000001</v>
+        <v>5.5594</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0867</v>
+        <v>4.9745</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0669</v>
+        <v>2.0213</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6914</v>
+        <v>1.6603</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0867</v>
+        <v>4.9745</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6307</v>
+        <v>2.6577</v>
       </c>
       <c r="G3" t="n">
-        <v>2.456</v>
+        <v>2.3168</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7856</v>
+        <v>3.5357</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0442</v>
+        <v>1.9852</v>
       </c>
       <c r="J3" t="n">
-        <v>2.456</v>
+        <v>2.3168</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>154</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5002</v>
+        <v>4.302</v>
       </c>
       <c r="N3" t="n">
         <v>256</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9865</v>
+        <v>3.9197</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6198</v>
+        <v>1.5927</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1905</v>
+        <v>1.1798</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9865</v>
+        <v>3.9197</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7756</v>
+        <v>2.7841</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2109</v>
+        <v>1.1356</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2636</v>
+        <v>4.0102</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3023</v>
+        <v>2.2516</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2109</v>
+        <v>1.1356</v>
       </c>
       <c r="K4" t="n">
         <v>102</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5132</v>
+        <v>3.3872</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.757</v>
+        <v>3.6414</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5266</v>
+        <v>1.4796</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0861</v>
+        <v>1.053</v>
       </c>
       <c r="E5" t="n">
-        <v>3.757</v>
+        <v>3.6414</v>
       </c>
       <c r="F5" t="n">
-        <v>2.865</v>
+        <v>2.8799</v>
       </c>
       <c r="G5" t="n">
-        <v>0.892</v>
+        <v>0.7615</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5586</v>
+        <v>4.3698</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4616</v>
+        <v>2.4535</v>
       </c>
       <c r="J5" t="n">
-        <v>0.892</v>
+        <v>0.7615</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3536</v>
+        <v>3.215</v>
       </c>
       <c r="N5" t="n">
         <v>218</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3843</v>
+        <v>3.4711</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3751</v>
+        <v>1.4104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9164</v>
+        <v>0.9755</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3843</v>
+        <v>3.4711</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3502</v>
+        <v>2.4309</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0341</v>
+        <v>1.0402</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8599</v>
+        <v>2.684</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5443</v>
+        <v>1.507</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0341</v>
+        <v>1.0402</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>185</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5784</v>
+        <v>2.5472</v>
       </c>
       <c r="N6" t="n">
         <v>232</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3219</v>
+        <v>3.3434</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3498</v>
+        <v>1.3585</v>
       </c>
       <c r="D7" t="n">
-        <v>0.888</v>
+        <v>0.9173</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3219</v>
+        <v>3.3434</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6712</v>
+        <v>2.7226</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6208</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9191</v>
+        <v>3.7794</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1163</v>
+        <v>2.122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6208</v>
       </c>
       <c r="K7" t="n">
         <v>47</v>
@@ -759,7 +759,7 @@
         <v>185</v>
       </c>
       <c r="M7" t="n">
-        <v>2.767</v>
+        <v>2.7428</v>
       </c>
       <c r="N7" t="n">
         <v>232</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0698</v>
+        <v>2.8496</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2473</v>
+        <v>1.1579</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7732</v>
+        <v>0.6923</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0698</v>
+        <v>2.8496</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5624</v>
+        <v>2.8166</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5074</v>
+        <v>0.033</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5624</v>
+        <v>4.1322</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8437</v>
+        <v>2.3201</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5074</v>
+        <v>0.033</v>
       </c>
       <c r="K8" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3511</v>
+        <v>2.3531</v>
       </c>
       <c r="N8" t="n">
-        <v>256</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8795</v>
+        <v>2.7989</v>
       </c>
       <c r="C9" t="n">
-        <v>1.17</v>
+        <v>1.1373</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6866</v>
+        <v>0.6692</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8795</v>
+        <v>2.7989</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8332</v>
+        <v>1.3112</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0463</v>
+        <v>1.4877</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4536</v>
+        <v>1.3112</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4049</v>
+        <v>0.7362</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0463</v>
+        <v>1.4877</v>
       </c>
       <c r="K9" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="L9" t="n">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4512</v>
+        <v>2.2239</v>
       </c>
       <c r="N9" t="n">
-        <v>218</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7874</v>
+        <v>2.7495</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1326</v>
+        <v>1.1172</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7874</v>
+        <v>2.7495</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7874</v>
+        <v>2.7495</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3759</v>
+        <v>3.351</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4629</v>
+        <v>3.4405</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4629</v>
+        <v>3.4405</v>
       </c>
       <c r="N10" t="n">
         <v>170</v>
@@ -906,323 +906,323 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4683</v>
+        <v>2.447</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0029</v>
+        <v>0.9943</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4994</v>
+        <v>0.5089</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4683</v>
+        <v>2.447</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4683</v>
+        <v>2.7093</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.2623</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6773</v>
+        <v>3.7293</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7463</v>
+        <v>2.0939</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.2623</v>
       </c>
       <c r="K11" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7463</v>
+        <v>1.8316</v>
       </c>
       <c r="N11" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3651</v>
+        <v>2.3997</v>
       </c>
       <c r="C12" t="n">
-        <v>0.961</v>
+        <v>0.9751</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4524</v>
+        <v>0.4874</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3651</v>
+        <v>2.3997</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9539</v>
+        <v>2.3997</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4112</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9539</v>
+        <v>2.5491</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0551</v>
+        <v>2.6173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4112</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="L12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4663</v>
+        <v>2.6173</v>
       </c>
       <c r="N12" t="n">
-        <v>256</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.362</v>
+        <v>2.1887</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9597</v>
+        <v>0.8893</v>
       </c>
       <c r="D13" t="n">
-        <v>0.451</v>
+        <v>0.3913</v>
       </c>
       <c r="E13" t="n">
-        <v>2.362</v>
+        <v>2.1887</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6595</v>
+        <v>2.1887</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2975</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8806</v>
+        <v>2.1887</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0955</v>
+        <v>2.1887</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2975</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.798</v>
+        <v>2.1887</v>
       </c>
       <c r="N13" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1687</v>
+        <v>2.0391</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8812</v>
+        <v>0.8285</v>
       </c>
       <c r="D14" t="n">
-        <v>0.363</v>
+        <v>0.3231</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1687</v>
+        <v>2.0391</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1687</v>
+        <v>1.6462</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.3929</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1687</v>
+        <v>1.6462</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1687</v>
+        <v>0.9243</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.3929</v>
       </c>
       <c r="K14" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1687</v>
+        <v>1.3172</v>
       </c>
       <c r="N14" t="n">
-        <v>119</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1163</v>
+        <v>2.0288</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8599</v>
+        <v>0.8244</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3392</v>
+        <v>0.3184</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1163</v>
+        <v>2.0288</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1438</v>
+        <v>2.6871</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0275</v>
+        <v>-0.6583</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1791</v>
+        <v>3.646</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1767</v>
+        <v>2.0471</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0275</v>
+        <v>-0.6583</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L15" t="n">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1492</v>
+        <v>1.3888</v>
       </c>
       <c r="N15" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8996</v>
+        <v>1.9682</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7719</v>
+        <v>0.7997</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2405</v>
+        <v>0.2908</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8996</v>
+        <v>1.9682</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6332</v>
+        <v>2.4855</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7336</v>
+        <v>-0.5173</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7936</v>
+        <v>2.8889</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0485</v>
+        <v>1.622</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7336</v>
+        <v>-0.5173</v>
       </c>
       <c r="K16" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L16" t="n">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3149</v>
+        <v>1.1047</v>
       </c>
       <c r="N16" t="n">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8495</v>
+        <v>1.9487</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2177</v>
+        <v>0.2819</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8495</v>
+        <v>1.9487</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3811</v>
+        <v>1.9666</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5316</v>
+        <v>-0.0179</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9619</v>
+        <v>1.9666</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5994</v>
+        <v>1.1042</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5316</v>
+        <v>-0.0179</v>
       </c>
       <c r="K17" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L17" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0678</v>
+        <v>1.0863</v>
       </c>
       <c r="N17" t="n">
-        <v>218</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7277</v>
+        <v>0.7227</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1911</v>
+        <v>0.2045</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7909</v>
+        <v>1.7787</v>
       </c>
       <c r="N18" t="n">
         <v>119</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6492</v>
+        <v>1.5531</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6701</v>
+        <v>0.6311</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1265</v>
+        <v>0.1017</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6492</v>
+        <v>1.5531</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6492</v>
+        <v>1.5531</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6492</v>
+        <v>1.5531</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6917</v>
+        <v>1.5946</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6917</v>
+        <v>1.5946</v>
       </c>
       <c r="N19" t="n">
         <v>170</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5154</v>
+        <v>1.4548</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6157</v>
+        <v>0.5911</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0569</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5154</v>
+        <v>1.4548</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5319</v>
+        <v>1.4904</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0165</v>
+        <v>-0.0356</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5319</v>
+        <v>1.4904</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8272</v>
+        <v>0.8368</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0165</v>
+        <v>-0.0356</v>
       </c>
       <c r="K20" t="n">
         <v>132</v>
@@ -1357,7 +1357,7 @@
         <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8107000000000001</v>
+        <v>0.8012</v>
       </c>
       <c r="N20" t="n">
         <v>218</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3936</v>
+        <v>1.3319</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5663</v>
+        <v>0.5412</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0102</v>
+        <v>0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3936</v>
+        <v>1.3319</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9896</v>
+        <v>0.9254</v>
       </c>
       <c r="G21" t="n">
-        <v>0.404</v>
+        <v>0.4065</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9896</v>
+        <v>0.9254</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5344</v>
+        <v>0.5196</v>
       </c>
       <c r="J21" t="n">
-        <v>0.404</v>
+        <v>0.4065</v>
       </c>
       <c r="K21" t="n">
         <v>102</v>
@@ -1403,7 +1403,7 @@
         <v>154</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9384</v>
+        <v>0.9260999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>256</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4951</v>
+        <v>0.5104</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0336</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2185</v>
+        <v>1.2561</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4053</v>
+        <v>0.4055</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1701</v>
+        <v>-0.1512</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="N23" t="n">
         <v>119</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9109</v>
+        <v>0.8822</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3701</v>
+        <v>0.3585</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2095</v>
+        <v>-0.2039</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9109</v>
+        <v>0.8822</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9109</v>
+        <v>0.8822</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9109</v>
+        <v>0.8822</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9344</v>
+        <v>0.9058</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9344</v>
+        <v>0.9058</v>
       </c>
       <c r="N24" t="n">
         <v>170</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8153</v>
+        <v>0.7612</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3313</v>
+        <v>0.3093</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2531</v>
+        <v>-0.259</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8153</v>
+        <v>0.7612</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8198</v>
+        <v>0.7612</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0045</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8198</v>
+        <v>0.7612</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4427</v>
+        <v>0.7612</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0045</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4382</v>
+        <v>0.7612</v>
       </c>
       <c r="N25" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3027</v>
+        <v>0.2782</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2851</v>
+        <v>-0.2939</v>
       </c>
       <c r="E26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="F26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="I26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.745</v>
+        <v>0.6846</v>
       </c>
       <c r="N26" t="n">
         <v>119</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.742</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3015</v>
+        <v>0.2579</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2864</v>
+        <v>-0.3167</v>
       </c>
       <c r="E27" t="n">
-        <v>0.742</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.742</v>
+        <v>0.6812</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0466</v>
       </c>
       <c r="H27" t="n">
-        <v>0.742</v>
+        <v>0.6812</v>
       </c>
       <c r="I27" t="n">
-        <v>0.742</v>
+        <v>0.3825</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0466</v>
       </c>
       <c r="K27" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>0.742</v>
+        <v>0.3359</v>
       </c>
       <c r="N27" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1914</v>
+        <v>0.1635</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4098</v>
+        <v>-0.4225</v>
       </c>
       <c r="E28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="F28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="I28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.471</v>
+        <v>0.4023</v>
       </c>
       <c r="N28" t="n">
         <v>96</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4149</v>
+        <v>0.3761</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1686</v>
+        <v>0.1528</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4353</v>
+        <v>-0.4345</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4149</v>
+        <v>0.3761</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6914</v>
       </c>
       <c r="G29" t="n">
-        <v>1.1231</v>
+        <v>1.0675</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6914</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3824</v>
+        <v>-0.3882</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1231</v>
+        <v>1.0675</v>
       </c>
       <c r="K29" t="n">
         <v>47</v>
@@ -1771,7 +1771,7 @@
         <v>185</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7406999999999999</v>
+        <v>0.6792999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>232</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3649</v>
+        <v>0.2992</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1483</v>
+        <v>0.1216</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4581</v>
+        <v>-0.4695</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3649</v>
+        <v>0.2992</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3649</v>
+        <v>0.2992</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3649</v>
+        <v>0.2992</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3743</v>
+        <v>0.3072</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3743</v>
+        <v>0.3072</v>
       </c>
       <c r="N30" t="n">
         <v>170</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1962</v>
+        <v>0.2049</v>
       </c>
       <c r="C31" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5349</v>
+        <v>-0.5124</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1962</v>
+        <v>0.2049</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1335</v>
+        <v>-0.1124</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3297</v>
+        <v>0.3173</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1335</v>
+        <v>-0.1124</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0721</v>
+        <v>-0.0631</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3297</v>
+        <v>0.3173</v>
       </c>
       <c r="K31" t="n">
         <v>58</v>
@@ -1863,7 +1863,7 @@
         <v>55</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2576</v>
+        <v>0.2542</v>
       </c>
       <c r="N31" t="n">
         <v>113</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0028</v>
+        <v>-0.0143</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6211</v>
+        <v>-0.6218</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0069</v>
+        <v>-0.0351</v>
       </c>
       <c r="N32" t="n">
         <v>68</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0249</v>
+        <v>-0.022</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6521</v>
+        <v>-0.6304</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0612</v>
+        <v>-0.0541</v>
       </c>
       <c r="N33" t="n">
         <v>68</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0993</v>
+        <v>-0.1283</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7355</v>
+        <v>-0.7496</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2444</v>
+        <v>-0.3158</v>
       </c>
       <c r="N34" t="n">
         <v>96</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1179</v>
+        <v>-0.1453</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7563</v>
+        <v>-0.7687</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3577</v>
       </c>
       <c r="N35" t="n">
         <v>96</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.306</v>
+        <v>-0.3015</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.967</v>
+        <v>-0.9438</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.753</v>
+        <v>-0.7419</v>
       </c>
       <c r="N36" t="n">
         <v>96</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3171</v>
+        <v>-0.3204</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9795</v>
+        <v>-0.965</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7805</v>
+        <v>-0.7886</v>
       </c>
       <c r="N37" t="n">
         <v>96</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0381</v>
+        <v>-1.0248</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4218</v>
+        <v>-0.4164</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0968</v>
+        <v>-1.0726</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0381</v>
+        <v>-1.0248</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6476</v>
+        <v>-0.6463</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.3905</v>
+        <v>-0.3785</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6476</v>
+        <v>-0.6463</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3497</v>
+        <v>-0.3629</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3905</v>
+        <v>-0.3785</v>
       </c>
       <c r="K38" t="n">
         <v>132</v>
@@ -2185,7 +2185,7 @@
         <v>86</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7402</v>
+        <v>-0.7414000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>218</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4552</v>
+        <v>-0.4479</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1342</v>
+        <v>-1.108</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1203</v>
+        <v>-1.1024</v>
       </c>
       <c r="N39" t="n">
         <v>68</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5442</v>
+        <v>-0.54</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2339</v>
+        <v>-1.2112</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3393</v>
+        <v>-1.3289</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4243</v>
+        <v>-1.396</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5787</v>
+        <v>-0.5672</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2726</v>
+        <v>-1.2417</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4243</v>
+        <v>-1.396</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7613</v>
+        <v>-0.7641</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.663</v>
+        <v>-0.6319</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7613</v>
+        <v>-0.7641</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4111</v>
+        <v>-0.429</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.663</v>
+        <v>-0.6319</v>
       </c>
       <c r="K41" t="n">
         <v>58</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0741</v>
+        <v>-1.0609</v>
       </c>
       <c r="N41" t="n">
         <v>113</v>
@@ -2429,10 +2429,10 @@
         <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5845</v>
+        <v>0.5137</v>
       </c>
       <c r="J2" t="n">
-        <v>15.7815</v>
+        <v>13.8699</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4768</v>
+        <v>0.4094</v>
       </c>
       <c r="J3" t="n">
-        <v>12.8736</v>
+        <v>11.0538</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0543</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8522</v>
+        <v>-1.4661</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2437</v>
+        <v>-1.8171</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1099</v>
+        <v>-0.092</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.9673</v>
+        <v>-2.484</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4357</v>
+        <v>0.4366</v>
       </c>
       <c r="J7" t="n">
-        <v>11.7639</v>
+        <v>11.7882</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0551</v>
+        <v>0.045</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4877</v>
+        <v>1.215</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.002</v>
+        <v>-0.0011</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.054</v>
+        <v>-0.0297</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0452</v>
+        <v>-0.0341</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2204</v>
+        <v>-0.9207</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.15</v>
+        <v>-0.1301</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.05</v>
+        <v>-3.5127</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J12" t="n">
-        <v>13.1652</v>
+        <v>11.2248</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1387</v>
+        <v>0.1052</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9932</v>
+        <v>3.7872</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.6168</v>
+        <v>-5.904</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2645</v>
+        <v>-0.2451</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.522</v>
+        <v>-8.823600000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2742</v>
+        <v>-0.2551</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.8712</v>
+        <v>-9.1836</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0098</v>
+        <v>1.0027</v>
       </c>
       <c r="J17" t="n">
-        <v>36.3528</v>
+        <v>36.0972</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7694</v>
+        <v>0.741</v>
       </c>
       <c r="J18" t="n">
-        <v>27.6984</v>
+        <v>26.676</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5855</v>
       </c>
       <c r="J19" t="n">
-        <v>22.374</v>
+        <v>21.078</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2836</v>
+        <v>-0.2434</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.2096</v>
+        <v>-8.7624</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7248</v>
+        <v>-0.696</v>
       </c>
       <c r="J21" t="n">
-        <v>-26.0928</v>
+        <v>-25.056</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.724</v>
+        <v>0.6673</v>
       </c>
       <c r="J22" t="n">
-        <v>26.064</v>
+        <v>24.0228</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6052</v>
       </c>
       <c r="J23" t="n">
-        <v>23.8968</v>
+        <v>21.7872</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1022</v>
+        <v>-0.0848</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6792</v>
+        <v>-3.0528</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.205</v>
+        <v>-0.1844</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.38</v>
+        <v>-6.6384</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3784</v>
+        <v>-0.3665</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.6224</v>
+        <v>-13.194</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.766</v>
+        <v>0.7378</v>
       </c>
       <c r="J27" t="n">
-        <v>27.576</v>
+        <v>26.5608</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4443</v>
+        <v>0.4014</v>
       </c>
       <c r="J28" t="n">
-        <v>15.9948</v>
+        <v>14.4504</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2877</v>
+        <v>-0.2477</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.3572</v>
+        <v>-8.917199999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.89</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3682</v>
+        <v>-0.3258</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.2552</v>
+        <v>-11.7288</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.77</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6198</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.6052</v>
+        <v>-22.3128</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4465</v>
+        <v>0.4539</v>
       </c>
       <c r="J32" t="n">
-        <v>12.502</v>
+        <v>12.7092</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4022</v>
+        <v>0.3995</v>
       </c>
       <c r="J33" t="n">
-        <v>11.2616</v>
+        <v>11.186</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.203</v>
+        <v>0.1884</v>
       </c>
       <c r="J34" t="n">
-        <v>5.684</v>
+        <v>5.2752</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1427</v>
+        <v>-0.123</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.9956</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.209</v>
+        <v>-0.1885</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.852</v>
+        <v>-5.278</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0784</v>
+        <v>0.0546</v>
       </c>
       <c r="J37" t="n">
-        <v>2.1952</v>
+        <v>1.5288</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0584</v>
+        <v>0.0392</v>
       </c>
       <c r="J38" t="n">
-        <v>1.6352</v>
+        <v>1.0976</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.02</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0584</v>
+        <v>0.0392</v>
       </c>
       <c r="J39" t="n">
-        <v>1.6352</v>
+        <v>1.0976</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0702</v>
+        <v>-0.0569</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.9656</v>
+        <v>-1.5932</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2686</v>
+        <v>-0.2491</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.5208</v>
+        <v>-6.9748</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5911</v>
+        <v>0.5793</v>
       </c>
       <c r="J42" t="n">
-        <v>17.733</v>
+        <v>17.379</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5097</v>
+        <v>0.4947</v>
       </c>
       <c r="J43" t="n">
-        <v>15.291</v>
+        <v>14.841</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4187</v>
+        <v>0.381</v>
       </c>
       <c r="J44" t="n">
-        <v>12.561</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3958</v>
+        <v>0.3577</v>
       </c>
       <c r="J45" t="n">
-        <v>11.874</v>
+        <v>10.731</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3915</v>
+        <v>-0.349</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.745</v>
+        <v>-10.47</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4066</v>
+        <v>0.3505</v>
       </c>
       <c r="J47" t="n">
-        <v>12.198</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.14</v>
       </c>
       <c r="I48" t="n">
-        <v>0.335</v>
+        <v>0.282</v>
       </c>
       <c r="J48" t="n">
-        <v>10.05</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0838</v>
+        <v>-0.0689</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.514</v>
+        <v>-2.067</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.326</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3722</v>
+        <v>-0.3591</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.166</v>
+        <v>-10.773</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.23</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5732</v>
+        <v>0.5626</v>
       </c>
       <c r="J52" t="n">
-        <v>16.0496</v>
+        <v>15.7528</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5571</v>
+        <v>0.5473</v>
       </c>
       <c r="J53" t="n">
-        <v>15.5988</v>
+        <v>15.3244</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2949</v>
+        <v>0.2605</v>
       </c>
       <c r="J54" t="n">
-        <v>8.257199999999999</v>
+        <v>7.294</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.06</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2114</v>
+        <v>0.1816</v>
       </c>
       <c r="J55" t="n">
-        <v>5.9192</v>
+        <v>5.0848</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1814</v>
+        <v>0.1538</v>
       </c>
       <c r="J56" t="n">
-        <v>5.0792</v>
+        <v>4.3064</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.19</v>
       </c>
       <c r="I57" t="n">
-        <v>0.427</v>
+        <v>0.3718</v>
       </c>
       <c r="J57" t="n">
-        <v>11.956</v>
+        <v>10.4104</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2003</v>
+        <v>0.1588</v>
       </c>
       <c r="J58" t="n">
-        <v>5.6084</v>
+        <v>4.4464</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0829</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.3212</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.83</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2178</v>
+        <v>-0.1974</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.0984</v>
+        <v>-5.5272</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3247</v>
+        <v>-0.3081</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.0916</v>
+        <v>-8.626799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0473</v>
+        <v>0.042</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9933</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.91</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1147</v>
+        <v>-0.1001</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.4087</v>
+        <v>-2.1021</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.74</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2887</v>
+        <v>-0.2718</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.0627</v>
+        <v>-5.7078</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3801</v>
+        <v>-0.3671</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.9821</v>
+        <v>-7.7091</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.398</v>
+        <v>-0.3863</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.358000000000001</v>
+        <v>-8.112299999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2708</v>
+        <v>1.2714</v>
       </c>
       <c r="J67" t="n">
-        <v>26.6868</v>
+        <v>26.6994</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.75</v>
       </c>
       <c r="I68" t="n">
-        <v>1.2342</v>
+        <v>1.2328</v>
       </c>
       <c r="J68" t="n">
-        <v>25.9182</v>
+        <v>25.8888</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.36</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7343</v>
+        <v>0.7271</v>
       </c>
       <c r="J69" t="n">
-        <v>15.4203</v>
+        <v>15.2691</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.19</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4759</v>
+        <v>0.4597</v>
       </c>
       <c r="J70" t="n">
-        <v>9.9939</v>
+        <v>9.653700000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.13</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3482</v>
+        <v>0.3156</v>
       </c>
       <c r="J71" t="n">
-        <v>7.3122</v>
+        <v>6.6276</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5891</v>
       </c>
       <c r="J72" t="n">
-        <v>21.0256</v>
+        <v>20.0294</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3756</v>
+        <v>0.3205</v>
       </c>
       <c r="J73" t="n">
-        <v>12.7704</v>
+        <v>10.897</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0599</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.5432</v>
+        <v>-2.0366</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1828</v>
+        <v>-0.1622</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.2152</v>
+        <v>-5.5148</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.265</v>
+        <v>-0.2456</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.01</v>
+        <v>-8.3504</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.41</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8554</v>
+        <v>0.8401</v>
       </c>
       <c r="J77" t="n">
-        <v>29.0836</v>
+        <v>28.5634</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.41</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8554</v>
+        <v>0.8401</v>
       </c>
       <c r="J78" t="n">
-        <v>29.0836</v>
+        <v>28.5634</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.24</v>
       </c>
       <c r="I79" t="n">
-        <v>0.596</v>
+        <v>0.5835</v>
       </c>
       <c r="J79" t="n">
-        <v>20.264</v>
+        <v>19.839</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.78</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6513</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-22.1442</v>
+        <v>-20.9576</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.0132</v>
+        <v>-1.0135</v>
       </c>
       <c r="J81" t="n">
-        <v>-34.4488</v>
+        <v>-34.459</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.88</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5181</v>
+        <v>1.5516</v>
       </c>
       <c r="J82" t="n">
-        <v>30.362</v>
+        <v>31.032</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1827</v>
+        <v>1.2033</v>
       </c>
       <c r="J83" t="n">
-        <v>23.654</v>
+        <v>24.066</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.59</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1705</v>
+        <v>1.1909</v>
       </c>
       <c r="J84" t="n">
-        <v>23.41</v>
+        <v>23.818</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.42</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9347</v>
+        <v>0.9363</v>
       </c>
       <c r="J85" t="n">
-        <v>18.694</v>
+        <v>18.726</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.31</v>
       </c>
       <c r="I86" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7095</v>
       </c>
       <c r="J86" t="n">
-        <v>14.506</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.78</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2209</v>
+        <v>-0.205</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.418</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2729</v>
+        <v>-0.2601</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.458</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3855</v>
+        <v>-0.3774</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.71</v>
+        <v>-7.548</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.515</v>
+        <v>-0.5148</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.3</v>
+        <v>-10.296</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.41</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5592</v>
+        <v>-0.5644</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.184</v>
+        <v>-11.288</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2913</v>
+        <v>0.2824</v>
       </c>
       <c r="J92" t="n">
-        <v>7.2825</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1782</v>
+        <v>-0.1607</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.455</v>
+        <v>-4.0175</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1983</v>
+        <v>-0.1802</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.9575</v>
+        <v>-4.505</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3136</v>
+        <v>-0.2965</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.84</v>
+        <v>-7.4125</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3778</v>
+        <v>-0.3645</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.445</v>
+        <v>-9.112500000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>0.659</v>
+        <v>0.5874</v>
       </c>
       <c r="J97" t="n">
-        <v>16.475</v>
+        <v>14.685</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5088</v>
+        <v>0.4423</v>
       </c>
       <c r="J98" t="n">
-        <v>12.72</v>
+        <v>11.0575</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.37</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4779</v>
+        <v>0.4132</v>
       </c>
       <c r="J99" t="n">
-        <v>11.9475</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2912</v>
+        <v>0.2418</v>
       </c>
       <c r="J100" t="n">
-        <v>7.28</v>
+        <v>6.045</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0653</v>
+        <v>0.0459</v>
       </c>
       <c r="J101" t="n">
-        <v>1.6325</v>
+        <v>1.1475</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.31</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7845</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>20.397</v>
+        <v>19.6976</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7019</v>
+        <v>0.6701</v>
       </c>
       <c r="J103" t="n">
-        <v>18.2494</v>
+        <v>17.4226</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5737</v>
+        <v>0.5373</v>
       </c>
       <c r="J104" t="n">
-        <v>14.9162</v>
+        <v>13.9698</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1784</v>
+        <v>0.1513</v>
       </c>
       <c r="J105" t="n">
-        <v>4.6384</v>
+        <v>3.9338</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3708</v>
+        <v>-0.3288</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.6408</v>
+        <v>-8.5488</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4982</v>
+        <v>0.4391</v>
       </c>
       <c r="J107" t="n">
-        <v>12.9532</v>
+        <v>11.4166</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1233</v>
+        <v>0.0934</v>
       </c>
       <c r="J108" t="n">
-        <v>3.2058</v>
+        <v>2.4284</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="J109" t="n">
-        <v>1.8824</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1591</v>
+        <v>-0.139</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.1366</v>
+        <v>-3.614</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.86</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1918</v>
+        <v>-0.1712</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.9868</v>
+        <v>-4.4512</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4232</v>
+        <v>1.4511</v>
       </c>
       <c r="J112" t="n">
-        <v>37.0032</v>
+        <v>37.7286</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>18.3326</v>
+        <v>17.6254</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3286</v>
+        <v>0.2962</v>
       </c>
       <c r="J114" t="n">
-        <v>8.5436</v>
+        <v>7.7012</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.249</v>
+        <v>0.2187</v>
       </c>
       <c r="J115" t="n">
-        <v>6.474</v>
+        <v>5.6862</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0183</v>
+        <v>0.0083</v>
       </c>
       <c r="J116" t="n">
-        <v>0.4758</v>
+        <v>0.2158</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.07</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2024</v>
+        <v>0.1606</v>
       </c>
       <c r="J117" t="n">
-        <v>5.2624</v>
+        <v>4.1756</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1806</v>
+        <v>0.1413</v>
       </c>
       <c r="J118" t="n">
-        <v>4.6956</v>
+        <v>3.6738</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1421</v>
+        <v>-0.1235</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.6946</v>
+        <v>-3.211</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1857</v>
+        <v>-0.1656</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.8282</v>
+        <v>-4.3056</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.227</v>
+        <v>-0.2068</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.902</v>
+        <v>-5.3768</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8153</v>
+        <v>0.7916</v>
       </c>
       <c r="J122" t="n">
-        <v>22.0131</v>
+        <v>21.3732</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7141</v>
+        <v>0.6845</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2807</v>
+        <v>18.4815</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.546</v>
+        <v>0.5114</v>
       </c>
       <c r="J124" t="n">
-        <v>14.742</v>
+        <v>13.8078</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.13</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3873</v>
+        <v>0.3527</v>
       </c>
       <c r="J125" t="n">
-        <v>10.4571</v>
+        <v>9.5229</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>0.028</v>
+        <v>0.0182</v>
       </c>
       <c r="J126" t="n">
-        <v>0.756</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2668</v>
+        <v>0.2188</v>
       </c>
       <c r="J127" t="n">
-        <v>7.2036</v>
+        <v>5.9076</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0206</v>
+        <v>-0.0153</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.5562</v>
+        <v>-0.4131</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0819</v>
+        <v>-0.068</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.2113</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2159</v>
+        <v>-0.1957</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.8293</v>
+        <v>-5.2839</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2559</v>
+        <v>-0.2362</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.9093</v>
+        <v>-6.3774</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.86</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1531</v>
+        <v>-0.1367</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.3682</v>
+        <v>-3.0074</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2973</v>
+        <v>-0.2842</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.5406</v>
+        <v>-6.2524</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3415</v>
+        <v>-0.3291</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.513</v>
+        <v>-7.2402</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.61</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3941</v>
+        <v>-0.3834</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.670199999999999</v>
+        <v>-8.434799999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.53</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4648</v>
+        <v>-0.4592</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.2256</v>
+        <v>-10.1024</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.11</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8102</v>
+        <v>1.8705</v>
       </c>
       <c r="J137" t="n">
-        <v>39.8244</v>
+        <v>41.151</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0541</v>
+        <v>1.0661</v>
       </c>
       <c r="J138" t="n">
-        <v>23.1902</v>
+        <v>23.4542</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5744</v>
       </c>
       <c r="J139" t="n">
-        <v>13.1846</v>
+        <v>12.6368</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.22</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5564</v>
+        <v>0.5296</v>
       </c>
       <c r="J140" t="n">
-        <v>12.2408</v>
+        <v>11.6512</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.11</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2991</v>
+        <v>0.2664</v>
       </c>
       <c r="J141" t="n">
-        <v>6.5802</v>
+        <v>5.8608</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.23</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3439</v>
+        <v>0.2849</v>
       </c>
       <c r="J142" t="n">
-        <v>9.629200000000001</v>
+        <v>7.9772</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2827</v>
+        <v>0.2296</v>
       </c>
       <c r="J143" t="n">
-        <v>7.9156</v>
+        <v>6.4288</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1492</v>
+        <v>0.1146</v>
       </c>
       <c r="J144" t="n">
-        <v>4.1776</v>
+        <v>3.2088</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1184</v>
+        <v>0.0892</v>
       </c>
       <c r="J145" t="n">
-        <v>3.3152</v>
+        <v>2.4976</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0806</v>
+        <v>-0.0649</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.2568</v>
+        <v>-1.8172</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.39</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5717</v>
+        <v>0.5926</v>
       </c>
       <c r="J147" t="n">
-        <v>16.0076</v>
+        <v>16.5928</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.22</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3625</v>
+        <v>0.3555</v>
       </c>
       <c r="J148" t="n">
-        <v>10.15</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.88</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1711</v>
+        <v>-0.1506</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.7908</v>
+        <v>-4.2168</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2342</v>
+        <v>-0.2139</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.5576</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.3948</v>
+        <v>-6.8516</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.25</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6148</v>
+        <v>0.5777</v>
       </c>
       <c r="J152" t="n">
-        <v>13.5256</v>
+        <v>12.7094</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2302</v>
+        <v>-0.2143</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.0644</v>
+        <v>-4.7146</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.6</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4125</v>
+        <v>-0.4021</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.074999999999999</v>
+        <v>-8.8462</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4303</v>
+        <v>-0.4214</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.4666</v>
+        <v>-9.270799999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4656</v>
+        <v>-0.4602</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.2432</v>
+        <v>-10.1244</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3323</v>
+        <v>1.3533</v>
       </c>
       <c r="J157" t="n">
-        <v>29.3106</v>
+        <v>29.7726</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0615</v>
+        <v>1.0719</v>
       </c>
       <c r="J158" t="n">
-        <v>23.353</v>
+        <v>23.5818</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9873</v>
+        <v>0.9876</v>
       </c>
       <c r="J159" t="n">
-        <v>21.7206</v>
+        <v>21.7272</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.2</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5221</v>
+        <v>0.4932</v>
       </c>
       <c r="J160" t="n">
-        <v>11.4862</v>
+        <v>10.8504</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0397</v>
+        <v>0.0217</v>
       </c>
       <c r="J161" t="n">
-        <v>0.8734</v>
+        <v>0.4774</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7806</v>
+        <v>0.7722</v>
       </c>
       <c r="J162" t="n">
-        <v>16.3926</v>
+        <v>16.2162</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.86</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1562</v>
+        <v>-0.1401</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.2802</v>
+        <v>-2.9421</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.52</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4754</v>
+        <v>-0.4709</v>
       </c>
       <c r="J164" t="n">
-        <v>-9.9834</v>
+        <v>-9.8889</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.41</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5715</v>
+        <v>-0.5795</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.0015</v>
+        <v>-12.1695</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6233</v>
+        <v>-0.64</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.0893</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.75</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3782</v>
+        <v>1.4024</v>
       </c>
       <c r="J167" t="n">
-        <v>28.9422</v>
+        <v>29.4504</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.63</v>
       </c>
       <c r="I168" t="n">
-        <v>1.2301</v>
+        <v>1.2486</v>
       </c>
       <c r="J168" t="n">
-        <v>25.8321</v>
+        <v>26.2206</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9105</v>
+        <v>0.9061</v>
       </c>
       <c r="J169" t="n">
-        <v>19.1205</v>
+        <v>19.0281</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8548</v>
+        <v>0.8461</v>
       </c>
       <c r="J170" t="n">
-        <v>17.9508</v>
+        <v>17.7681</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.16</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4173</v>
+        <v>0.3857</v>
       </c>
       <c r="J171" t="n">
-        <v>8.763299999999999</v>
+        <v>8.0997</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.89</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1374</v>
+        <v>-0.1221</v>
       </c>
       <c r="J172" t="n">
-        <v>-3.0228</v>
+        <v>-2.6862</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1488</v>
+        <v>-0.1333</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.2736</v>
+        <v>-2.9326</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2128</v>
+        <v>-0.1964</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.6816</v>
+        <v>-4.3208</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3249</v>
+        <v>-0.3091</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.1478</v>
+        <v>-6.8002</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.424</v>
+        <v>-0.4146</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.327999999999999</v>
+        <v>-9.1212</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1193</v>
+        <v>1.1327</v>
       </c>
       <c r="J177" t="n">
-        <v>24.6246</v>
+        <v>24.9194</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9917</v>
+        <v>0.9912</v>
       </c>
       <c r="J178" t="n">
-        <v>21.8174</v>
+        <v>21.8064</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.38</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8863</v>
+        <v>0.8738</v>
       </c>
       <c r="J179" t="n">
-        <v>19.4986</v>
+        <v>19.2236</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4592</v>
+        <v>0.4283</v>
       </c>
       <c r="J180" t="n">
-        <v>10.1024</v>
+        <v>9.422599999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4592</v>
+        <v>0.4283</v>
       </c>
       <c r="J181" t="n">
-        <v>10.1024</v>
+        <v>9.422599999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2547</v>
+        <v>1.2756</v>
       </c>
       <c r="J182" t="n">
-        <v>42.6598</v>
+        <v>43.3704</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6277</v>
+        <v>0.5911</v>
       </c>
       <c r="J183" t="n">
-        <v>21.3418</v>
+        <v>20.0974</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.299</v>
+        <v>0.2629</v>
       </c>
       <c r="J184" t="n">
-        <v>10.166</v>
+        <v>8.938599999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3877</v>
+        <v>-0.3449</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.1818</v>
+        <v>-11.7266</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8491</v>
+        <v>-0.8307</v>
       </c>
       <c r="J186" t="n">
-        <v>-28.8694</v>
+        <v>-28.2438</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.254</v>
+        <v>0.2072</v>
       </c>
       <c r="J187" t="n">
-        <v>8.635999999999999</v>
+        <v>7.0448</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0422</v>
+        <v>-0.0322</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.4348</v>
+        <v>-1.0948</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.98</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0422</v>
+        <v>-0.0322</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.4348</v>
+        <v>-1.0948</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.907</v>
+        <v>-2.3766</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.907</v>
+        <v>-2.3766</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J192" t="n">
-        <v>7.2927</v>
+        <v>5.9967</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1465</v>
+        <v>0.1129</v>
       </c>
       <c r="J193" t="n">
-        <v>3.9555</v>
+        <v>3.0483</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0988</v>
+        <v>0.0732</v>
       </c>
       <c r="J194" t="n">
-        <v>2.6676</v>
+        <v>1.9764</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0998</v>
+        <v>-0.0828</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.6946</v>
+        <v>-2.2356</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.92</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1245</v>
+        <v>-0.1058</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.3615</v>
+        <v>-2.8566</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5849</v>
+        <v>0.5454</v>
       </c>
       <c r="J197" t="n">
-        <v>15.7923</v>
+        <v>14.7258</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5384</v>
+        <v>0.4973</v>
       </c>
       <c r="J198" t="n">
-        <v>14.5368</v>
+        <v>13.4271</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5148</v>
+        <v>0.473</v>
       </c>
       <c r="J199" t="n">
-        <v>13.8996</v>
+        <v>12.771</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1367</v>
+        <v>-0.1084</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.6909</v>
+        <v>-2.9268</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.179</v>
+        <v>-1.2004</v>
       </c>
       <c r="J201" t="n">
-        <v>-31.833</v>
+        <v>-32.4108</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.34</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8408</v>
+        <v>0.8183</v>
       </c>
       <c r="J202" t="n">
-        <v>20.1792</v>
+        <v>19.6392</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.549</v>
+        <v>0.5131</v>
       </c>
       <c r="J203" t="n">
-        <v>13.176</v>
+        <v>12.3144</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.438</v>
+        <v>0.4017</v>
       </c>
       <c r="J204" t="n">
-        <v>10.512</v>
+        <v>9.6408</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3156</v>
+        <v>0.2818</v>
       </c>
       <c r="J205" t="n">
-        <v>7.5744</v>
+        <v>6.7632</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1437</v>
+        <v>0.1196</v>
       </c>
       <c r="J206" t="n">
-        <v>3.4488</v>
+        <v>2.8704</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4443</v>
+        <v>0.387</v>
       </c>
       <c r="J207" t="n">
-        <v>10.6632</v>
+        <v>9.288</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1774</v>
+        <v>0.1386</v>
       </c>
       <c r="J208" t="n">
-        <v>4.2576</v>
+        <v>3.3264</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1548</v>
+        <v>0.1191</v>
       </c>
       <c r="J209" t="n">
-        <v>3.7152</v>
+        <v>2.8584</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2779</v>
+        <v>-0.2588</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.6696</v>
+        <v>-6.2112</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.71</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3346</v>
+        <v>-0.3186</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.0304</v>
+        <v>-7.6464</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.07</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2276</v>
+        <v>0.1854</v>
       </c>
       <c r="J212" t="n">
-        <v>5.4624</v>
+        <v>4.4496</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1818</v>
+        <v>0.1445</v>
       </c>
       <c r="J213" t="n">
-        <v>4.3632</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.04</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1575</v>
+        <v>0.1232</v>
       </c>
       <c r="J214" t="n">
-        <v>3.78</v>
+        <v>2.9568</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.203200000000001</v>
+        <v>-7.8264</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.38</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6118</v>
+        <v>-0.6289</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.6832</v>
+        <v>-15.0936</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4061</v>
+        <v>1.4316</v>
       </c>
       <c r="J217" t="n">
-        <v>33.7464</v>
+        <v>34.3584</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9263</v>
+        <v>0.9161</v>
       </c>
       <c r="J218" t="n">
-        <v>22.2312</v>
+        <v>21.9864</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.33</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7947</v>
+        <v>0.7755</v>
       </c>
       <c r="J219" t="n">
-        <v>19.0728</v>
+        <v>18.612</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.32</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7556</v>
       </c>
       <c r="J220" t="n">
-        <v>18.6168</v>
+        <v>18.1344</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6887</v>
+        <v>-0.6624</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.5288</v>
+        <v>-15.8976</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.92</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.0978</v>
+        <v>-0.0835</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.2494</v>
+        <v>-1.9205</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1102</v>
+        <v>-0.0955</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.5346</v>
+        <v>-2.1965</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2205</v>
+        <v>-0.2045</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.0715</v>
+        <v>-4.7035</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3949</v>
+        <v>-0.3831</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.082700000000001</v>
+        <v>-8.811299999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.52</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4833</v>
+        <v>-0.48</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.1159</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2538</v>
+        <v>1.2716</v>
       </c>
       <c r="J227" t="n">
-        <v>28.8374</v>
+        <v>29.2468</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.19</v>
+        <v>1.2059</v>
       </c>
       <c r="J228" t="n">
-        <v>27.37</v>
+        <v>27.7357</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.32</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7514</v>
       </c>
       <c r="J229" t="n">
-        <v>17.6778</v>
+        <v>17.2822</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.27</v>
       </c>
       <c r="I230" t="n">
-        <v>0.6687</v>
+        <v>0.6462</v>
       </c>
       <c r="J230" t="n">
-        <v>15.3801</v>
+        <v>14.8626</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.11</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3063</v>
+        <v>0.2742</v>
       </c>
       <c r="J231" t="n">
-        <v>7.0449</v>
+        <v>6.3066</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2869</v>
+        <v>1.3072</v>
       </c>
       <c r="J232" t="n">
-        <v>32.1725</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3654</v>
+        <v>0.3305</v>
       </c>
       <c r="J233" t="n">
-        <v>9.135</v>
+        <v>8.262499999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2613</v>
+        <v>0.2297</v>
       </c>
       <c r="J234" t="n">
-        <v>6.5325</v>
+        <v>5.7425</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2044</v>
+        <v>0.1758</v>
       </c>
       <c r="J235" t="n">
-        <v>5.11</v>
+        <v>4.395</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1665</v>
+        <v>-0.135</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.1625</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>1.111</v>
+        <v>1.1053</v>
       </c>
       <c r="J237" t="n">
-        <v>27.775</v>
+        <v>27.6325</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6197</v>
+        <v>0.5618</v>
       </c>
       <c r="J238" t="n">
-        <v>15.4925</v>
+        <v>14.045</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.65</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3911</v>
+        <v>-0.3798</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.7775</v>
+        <v>-9.494999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4</v>
+        <v>-0.3896</v>
       </c>
       <c r="J240" t="n">
-        <v>-10</v>
+        <v>-9.74</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.62</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4178</v>
+        <v>-0.4092</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.445</v>
+        <v>-10.23</v>
       </c>
     </row>
   </sheetData>
